--- a/results/CB/CorrectedResponses.xlsx
+++ b/results/CB/CorrectedResponses.xlsx
@@ -30071,47 +30071,47 @@
     </row>
     <row r="1186">
       <c r="A1186" t="n">
-        <v>1469</v>
+        <v>1530</v>
       </c>
       <c r="B1186" t="n">
-        <v>2574</v>
+        <v>2715</v>
       </c>
       <c r="C1186" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D1186" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1186" t="n">
-        <v>13.078219</v>
+        <v>15.25</v>
       </c>
       <c r="F1186" s="2" t="n">
-        <v>45244.81056145292</v>
+        <v>45245.20253195269</v>
       </c>
       <c r="G1186" t="inlineStr">
         <is>
-          <t>Corrected: ResponseTime to NULL</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="n">
-        <v>1530</v>
+        <v>1536</v>
       </c>
       <c r="B1187" t="n">
-        <v>2715</v>
+        <v>2731</v>
       </c>
       <c r="C1187" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D1187" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1187" t="n">
-        <v>15.25</v>
+        <v>9.49</v>
       </c>
       <c r="F1187" s="2" t="n">
-        <v>45245.20253195269</v>
+        <v>45245.23698837094</v>
       </c>
       <c r="G1187" t="inlineStr">
         <is>
@@ -30121,22 +30121,22 @@
     </row>
     <row r="1188">
       <c r="A1188" t="n">
-        <v>1536</v>
+        <v>1570</v>
       </c>
       <c r="B1188" t="n">
-        <v>2731</v>
+        <v>2812</v>
       </c>
       <c r="C1188" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D1188" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E1188" t="n">
-        <v>9.49</v>
+        <v>11.85</v>
       </c>
       <c r="F1188" s="2" t="n">
-        <v>45245.23698837094</v>
+        <v>45245.97316194134</v>
       </c>
       <c r="G1188" t="inlineStr">
         <is>
@@ -30146,22 +30146,22 @@
     </row>
     <row r="1189">
       <c r="A1189" t="n">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B1189" t="n">
-        <v>2812</v>
+        <v>2813</v>
       </c>
       <c r="C1189" t="n">
         <v>160</v>
       </c>
       <c r="D1189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1189" t="n">
-        <v>11.85</v>
+        <v>18.88</v>
       </c>
       <c r="F1189" s="2" t="n">
-        <v>45245.97316194134</v>
+        <v>45245.97406437432</v>
       </c>
       <c r="G1189" t="inlineStr">
         <is>
@@ -30171,22 +30171,22 @@
     </row>
     <row r="1190">
       <c r="A1190" t="n">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B1190" t="n">
-        <v>2813</v>
+        <v>2815</v>
       </c>
       <c r="C1190" t="n">
         <v>160</v>
       </c>
       <c r="D1190" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E1190" t="n">
-        <v>18.88</v>
+        <v>10.94</v>
       </c>
       <c r="F1190" s="2" t="n">
-        <v>45245.97406437432</v>
+        <v>45245.97515698333</v>
       </c>
       <c r="G1190" t="inlineStr">
         <is>
@@ -30196,22 +30196,22 @@
     </row>
     <row r="1191">
       <c r="A1191" t="n">
-        <v>1572</v>
+        <v>1577</v>
       </c>
       <c r="B1191" t="n">
-        <v>2815</v>
+        <v>2826</v>
       </c>
       <c r="C1191" t="n">
         <v>160</v>
       </c>
       <c r="D1191" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E1191" t="n">
-        <v>10.94</v>
+        <v>30</v>
       </c>
       <c r="F1191" s="2" t="n">
-        <v>45245.97515698333</v>
+        <v>45245.98421429555</v>
       </c>
       <c r="G1191" t="inlineStr">
         <is>
@@ -30221,22 +30221,22 @@
     </row>
     <row r="1192">
       <c r="A1192" t="n">
-        <v>1577</v>
+        <v>1597</v>
       </c>
       <c r="B1192" t="n">
-        <v>2826</v>
+        <v>2872</v>
       </c>
       <c r="C1192" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D1192" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E1192" t="n">
-        <v>30</v>
+        <v>10.01</v>
       </c>
       <c r="F1192" s="2" t="n">
-        <v>45245.98421429555</v>
+        <v>45246.38545727215</v>
       </c>
       <c r="G1192" t="inlineStr">
         <is>
@@ -30246,22 +30246,22 @@
     </row>
     <row r="1193">
       <c r="A1193" t="n">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B1193" t="n">
-        <v>2872</v>
+        <v>2874</v>
       </c>
       <c r="C1193" t="n">
         <v>164</v>
       </c>
       <c r="D1193" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1193" t="n">
-        <v>10.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F1193" s="2" t="n">
-        <v>45246.38545727215</v>
+        <v>45246.38723355257</v>
       </c>
       <c r="G1193" t="inlineStr">
         <is>
@@ -30271,22 +30271,22 @@
     </row>
     <row r="1194">
       <c r="A1194" t="n">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1194" t="n">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="C1194" t="n">
         <v>164</v>
       </c>
       <c r="D1194" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1194" t="n">
-        <v>9.800000000000001</v>
+        <v>20.87</v>
       </c>
       <c r="F1194" s="2" t="n">
-        <v>45246.38723355257</v>
+        <v>45246.38822015277</v>
       </c>
       <c r="G1194" t="inlineStr">
         <is>
@@ -30296,22 +30296,22 @@
     </row>
     <row r="1195">
       <c r="A1195" t="n">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="B1195" t="n">
-        <v>2875</v>
+        <v>2878</v>
       </c>
       <c r="C1195" t="n">
         <v>164</v>
       </c>
       <c r="D1195" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1195" t="n">
-        <v>20.87</v>
+        <v>10.57</v>
       </c>
       <c r="F1195" s="2" t="n">
-        <v>45246.38822015277</v>
+        <v>45246.38994094116</v>
       </c>
       <c r="G1195" t="inlineStr">
         <is>
@@ -30321,22 +30321,22 @@
     </row>
     <row r="1196">
       <c r="A1196" t="n">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="B1196" t="n">
-        <v>2878</v>
+        <v>2883</v>
       </c>
       <c r="C1196" t="n">
         <v>164</v>
       </c>
       <c r="D1196" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E1196" t="n">
-        <v>10.57</v>
+        <v>13.46</v>
       </c>
       <c r="F1196" s="2" t="n">
-        <v>45246.38994094116</v>
+        <v>45246.39422212101</v>
       </c>
       <c r="G1196" t="inlineStr">
         <is>
@@ -30346,22 +30346,22 @@
     </row>
     <row r="1197">
       <c r="A1197" t="n">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="B1197" t="n">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="C1197" t="n">
         <v>164</v>
       </c>
       <c r="D1197" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1197" t="n">
-        <v>13.46</v>
+        <v>8.49</v>
       </c>
       <c r="F1197" s="2" t="n">
-        <v>45246.39422212101</v>
+        <v>45246.39476618616</v>
       </c>
       <c r="G1197" t="inlineStr">
         <is>
@@ -30371,22 +30371,22 @@
     </row>
     <row r="1198">
       <c r="A1198" t="n">
-        <v>1604</v>
+        <v>1645</v>
       </c>
       <c r="B1198" t="n">
-        <v>2884</v>
+        <v>2962</v>
       </c>
       <c r="C1198" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D1198" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E1198" t="n">
-        <v>8.49</v>
+        <v>11.01</v>
       </c>
       <c r="F1198" s="2" t="n">
-        <v>45246.39476618616</v>
+        <v>45246.65972760375</v>
       </c>
       <c r="G1198" t="inlineStr">
         <is>
@@ -30396,22 +30396,22 @@
     </row>
     <row r="1199">
       <c r="A1199" t="n">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="B1199" t="n">
-        <v>2962</v>
+        <v>2966</v>
       </c>
       <c r="C1199" t="n">
         <v>170</v>
       </c>
       <c r="D1199" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E1199" t="n">
-        <v>11.01</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="F1199" s="2" t="n">
-        <v>45246.65972760375</v>
+        <v>45246.6620723353</v>
       </c>
       <c r="G1199" t="inlineStr">
         <is>
@@ -30421,22 +30421,22 @@
     </row>
     <row r="1200">
       <c r="A1200" t="n">
-        <v>1647</v>
+        <v>1650</v>
       </c>
       <c r="B1200" t="n">
-        <v>2966</v>
+        <v>2973</v>
       </c>
       <c r="C1200" t="n">
         <v>170</v>
       </c>
       <c r="D1200" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E1200" t="n">
-        <v>9.869999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="F1200" s="2" t="n">
-        <v>45246.6620723353</v>
+        <v>45246.66668340648</v>
       </c>
       <c r="G1200" t="inlineStr">
         <is>
@@ -30446,22 +30446,22 @@
     </row>
     <row r="1201">
       <c r="A1201" t="n">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B1201" t="n">
-        <v>2973</v>
+        <v>2975</v>
       </c>
       <c r="C1201" t="n">
         <v>170</v>
       </c>
       <c r="D1201" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1201" t="n">
-        <v>10.2</v>
+        <v>11.39</v>
       </c>
       <c r="F1201" s="2" t="n">
-        <v>45246.66668340648</v>
+        <v>45246.66821096941</v>
       </c>
       <c r="G1201" t="inlineStr">
         <is>
@@ -30471,22 +30471,22 @@
     </row>
     <row r="1202">
       <c r="A1202" t="n">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="B1202" t="n">
-        <v>2975</v>
+        <v>2977</v>
       </c>
       <c r="C1202" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D1202" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E1202" t="n">
-        <v>11.39</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="F1202" s="2" t="n">
-        <v>45246.66821096941</v>
+        <v>45246.74725903512</v>
       </c>
       <c r="G1202" t="inlineStr">
         <is>
@@ -30496,22 +30496,22 @@
     </row>
     <row r="1203">
       <c r="A1203" t="n">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B1203" t="n">
-        <v>2977</v>
+        <v>2978</v>
       </c>
       <c r="C1203" t="n">
         <v>171</v>
       </c>
       <c r="D1203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1203" t="n">
-        <v>9.289999999999999</v>
+        <v>30</v>
       </c>
       <c r="F1203" s="2" t="n">
-        <v>45246.74725903512</v>
+        <v>45246.74744415817</v>
       </c>
       <c r="G1203" t="inlineStr">
         <is>
@@ -30521,22 +30521,22 @@
     </row>
     <row r="1204">
       <c r="A1204" t="n">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="B1204" t="n">
-        <v>2978</v>
+        <v>2981</v>
       </c>
       <c r="C1204" t="n">
         <v>171</v>
       </c>
       <c r="D1204" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E1204" t="n">
-        <v>30</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="F1204" s="2" t="n">
-        <v>45246.74744415817</v>
+        <v>45246.74861468578</v>
       </c>
       <c r="G1204" t="inlineStr">
         <is>
@@ -30546,22 +30546,22 @@
     </row>
     <row r="1205">
       <c r="A1205" t="n">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="B1205" t="n">
-        <v>2981</v>
+        <v>2983</v>
       </c>
       <c r="C1205" t="n">
         <v>171</v>
       </c>
       <c r="D1205" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1205" t="n">
-        <v>9.869999999999999</v>
+        <v>30</v>
       </c>
       <c r="F1205" s="2" t="n">
-        <v>45246.74861468578</v>
+        <v>45246.75039967555</v>
       </c>
       <c r="G1205" t="inlineStr">
         <is>
@@ -30571,22 +30571,22 @@
     </row>
     <row r="1206">
       <c r="A1206" t="n">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="B1206" t="n">
-        <v>2983</v>
+        <v>2987</v>
       </c>
       <c r="C1206" t="n">
         <v>171</v>
       </c>
       <c r="D1206" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E1206" t="n">
         <v>30</v>
       </c>
       <c r="F1206" s="2" t="n">
-        <v>45246.75039967555</v>
+        <v>45246.75271800184</v>
       </c>
       <c r="G1206" t="inlineStr">
         <is>
@@ -30596,22 +30596,22 @@
     </row>
     <row r="1207">
       <c r="A1207" t="n">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="B1207" t="n">
-        <v>2987</v>
+        <v>2988</v>
       </c>
       <c r="C1207" t="n">
         <v>171</v>
       </c>
       <c r="D1207" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1207" t="n">
-        <v>30</v>
+        <v>9.43</v>
       </c>
       <c r="F1207" s="2" t="n">
-        <v>45246.75271800184</v>
+        <v>45246.75321231485</v>
       </c>
       <c r="G1207" t="inlineStr">
         <is>
@@ -30621,22 +30621,22 @@
     </row>
     <row r="1208">
       <c r="A1208" t="n">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B1208" t="n">
-        <v>2988</v>
+        <v>2990</v>
       </c>
       <c r="C1208" t="n">
         <v>171</v>
       </c>
       <c r="D1208" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1208" t="n">
-        <v>9.43</v>
+        <v>9.66</v>
       </c>
       <c r="F1208" s="2" t="n">
-        <v>45246.75321231485</v>
+        <v>45246.75460966777</v>
       </c>
       <c r="G1208" t="inlineStr">
         <is>
@@ -30646,22 +30646,22 @@
     </row>
     <row r="1209">
       <c r="A1209" t="n">
-        <v>1660</v>
+        <v>1667</v>
       </c>
       <c r="B1209" t="n">
-        <v>2990</v>
+        <v>3007</v>
       </c>
       <c r="C1209" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D1209" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E1209" t="n">
-        <v>9.66</v>
+        <v>10.14</v>
       </c>
       <c r="F1209" s="2" t="n">
-        <v>45246.75460966777</v>
+        <v>45246.85536228023</v>
       </c>
       <c r="G1209" t="inlineStr">
         <is>
@@ -30671,22 +30671,22 @@
     </row>
     <row r="1210">
       <c r="A1210" t="n">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="B1210" t="n">
-        <v>3007</v>
+        <v>3012</v>
       </c>
       <c r="C1210" t="n">
         <v>173</v>
       </c>
       <c r="D1210" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E1210" t="n">
-        <v>10.14</v>
+        <v>10.87</v>
       </c>
       <c r="F1210" s="2" t="n">
-        <v>45246.85536228023</v>
+        <v>45246.85893970131</v>
       </c>
       <c r="G1210" t="inlineStr">
         <is>
@@ -30696,22 +30696,22 @@
     </row>
     <row r="1211">
       <c r="A1211" t="n">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="B1211" t="n">
-        <v>3012</v>
+        <v>3018</v>
       </c>
       <c r="C1211" t="n">
         <v>173</v>
       </c>
       <c r="D1211" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E1211" t="n">
         <v>10.87</v>
       </c>
       <c r="F1211" s="2" t="n">
-        <v>45246.85893970131</v>
+        <v>45246.86313866416</v>
       </c>
       <c r="G1211" t="inlineStr">
         <is>
@@ -30721,22 +30721,22 @@
     </row>
     <row r="1212">
       <c r="A1212" t="n">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="B1212" t="n">
-        <v>3018</v>
+        <v>3022</v>
       </c>
       <c r="C1212" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D1212" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E1212" t="n">
-        <v>10.87</v>
+        <v>7.99</v>
       </c>
       <c r="F1212" s="2" t="n">
-        <v>45246.86313866416</v>
+        <v>45246.88879245762</v>
       </c>
       <c r="G1212" t="inlineStr">
         <is>
@@ -30746,22 +30746,22 @@
     </row>
     <row r="1213">
       <c r="A1213" t="n">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B1213" t="n">
-        <v>3022</v>
+        <v>3023</v>
       </c>
       <c r="C1213" t="n">
         <v>174</v>
       </c>
       <c r="D1213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1213" t="n">
-        <v>7.99</v>
+        <v>30</v>
       </c>
       <c r="F1213" s="2" t="n">
-        <v>45246.88879245762</v>
+        <v>45246.88976528713</v>
       </c>
       <c r="G1213" t="inlineStr">
         <is>
@@ -30771,22 +30771,22 @@
     </row>
     <row r="1214">
       <c r="A1214" t="n">
-        <v>1674</v>
+        <v>1678</v>
       </c>
       <c r="B1214" t="n">
-        <v>3023</v>
+        <v>3028</v>
       </c>
       <c r="C1214" t="n">
         <v>174</v>
       </c>
       <c r="D1214" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E1214" t="n">
-        <v>30</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="F1214" s="2" t="n">
-        <v>45246.88976528713</v>
+        <v>45246.89300805015</v>
       </c>
       <c r="G1214" t="inlineStr">
         <is>
@@ -30796,22 +30796,22 @@
     </row>
     <row r="1215">
       <c r="A1215" t="n">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B1215" t="n">
-        <v>3028</v>
+        <v>3031</v>
       </c>
       <c r="C1215" t="n">
         <v>174</v>
       </c>
       <c r="D1215" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1215" t="n">
-        <v>9.550000000000001</v>
+        <v>10.13</v>
       </c>
       <c r="F1215" s="2" t="n">
-        <v>45246.89300805015</v>
+        <v>45246.89526973582</v>
       </c>
       <c r="G1215" t="inlineStr">
         <is>
@@ -30821,22 +30821,22 @@
     </row>
     <row r="1216">
       <c r="A1216" t="n">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B1216" t="n">
-        <v>3031</v>
+        <v>3034</v>
       </c>
       <c r="C1216" t="n">
         <v>174</v>
       </c>
       <c r="D1216" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E1216" t="n">
-        <v>10.13</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="F1216" s="2" t="n">
-        <v>45246.89526973582</v>
+        <v>45246.89749475177</v>
       </c>
       <c r="G1216" t="inlineStr">
         <is>
@@ -30846,22 +30846,22 @@
     </row>
     <row r="1217">
       <c r="A1217" t="n">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B1217" t="n">
-        <v>3034</v>
+        <v>3037</v>
       </c>
       <c r="C1217" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D1217" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E1217" t="n">
-        <v>9.630000000000001</v>
+        <v>8.23</v>
       </c>
       <c r="F1217" s="2" t="n">
-        <v>45246.89749475177</v>
+        <v>45246.91916123396</v>
       </c>
       <c r="G1217" t="inlineStr">
         <is>
@@ -30871,22 +30871,22 @@
     </row>
     <row r="1218">
       <c r="A1218" t="n">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B1218" t="n">
-        <v>3037</v>
+        <v>3038</v>
       </c>
       <c r="C1218" t="n">
         <v>175</v>
       </c>
       <c r="D1218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1218" t="n">
-        <v>8.23</v>
+        <v>25.39</v>
       </c>
       <c r="F1218" s="2" t="n">
-        <v>45246.91916123396</v>
+        <v>45246.91997735655</v>
       </c>
       <c r="G1218" t="inlineStr">
         <is>
@@ -30896,22 +30896,22 @@
     </row>
     <row r="1219">
       <c r="A1219" t="n">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B1219" t="n">
-        <v>3038</v>
+        <v>3039</v>
       </c>
       <c r="C1219" t="n">
         <v>175</v>
       </c>
       <c r="D1219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1219" t="n">
-        <v>25.39</v>
+        <v>8.16</v>
       </c>
       <c r="F1219" s="2" t="n">
-        <v>45246.91997735655</v>
+        <v>45246.92046205697</v>
       </c>
       <c r="G1219" t="inlineStr">
         <is>
@@ -30921,22 +30921,22 @@
     </row>
     <row r="1220">
       <c r="A1220" t="n">
-        <v>1683</v>
+        <v>1685</v>
       </c>
       <c r="B1220" t="n">
-        <v>3039</v>
+        <v>3043</v>
       </c>
       <c r="C1220" t="n">
         <v>175</v>
       </c>
       <c r="D1220" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1220" t="n">
-        <v>8.16</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F1220" s="2" t="n">
-        <v>45246.92046205697</v>
+        <v>45246.92328370611</v>
       </c>
       <c r="G1220" t="inlineStr">
         <is>
@@ -30946,22 +30946,22 @@
     </row>
     <row r="1221">
       <c r="A1221" t="n">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="B1221" t="n">
-        <v>3043</v>
+        <v>3049</v>
       </c>
       <c r="C1221" t="n">
         <v>175</v>
       </c>
       <c r="D1221" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E1221" t="n">
-        <v>9.140000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="F1221" s="2" t="n">
-        <v>45246.92328370611</v>
+        <v>45246.92730989179</v>
       </c>
       <c r="G1221" t="inlineStr">
         <is>
@@ -30971,22 +30971,22 @@
     </row>
     <row r="1222">
       <c r="A1222" t="n">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B1222" t="n">
-        <v>3049</v>
+        <v>3052</v>
       </c>
       <c r="C1222" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D1222" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E1222" t="n">
-        <v>9.08</v>
+        <v>7.62</v>
       </c>
       <c r="F1222" s="2" t="n">
-        <v>45246.92730989179</v>
+        <v>45247.00002677304</v>
       </c>
       <c r="G1222" t="inlineStr">
         <is>
@@ -30996,22 +30996,22 @@
     </row>
     <row r="1223">
       <c r="A1223" t="n">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1223" t="n">
-        <v>3052</v>
+        <v>3053</v>
       </c>
       <c r="C1223" t="n">
         <v>176</v>
       </c>
       <c r="D1223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1223" t="n">
-        <v>7.62</v>
+        <v>15.96</v>
       </c>
       <c r="F1223" s="2" t="n">
-        <v>45247.00002677304</v>
+        <v>45247.00102358646</v>
       </c>
       <c r="G1223" t="inlineStr">
         <is>
@@ -31021,22 +31021,22 @@
     </row>
     <row r="1224">
       <c r="A1224" t="n">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B1224" t="n">
-        <v>3053</v>
+        <v>3054</v>
       </c>
       <c r="C1224" t="n">
         <v>176</v>
       </c>
       <c r="D1224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1224" t="n">
-        <v>15.96</v>
+        <v>8.56</v>
       </c>
       <c r="F1224" s="2" t="n">
-        <v>45247.00102358646</v>
+        <v>45247.00141032288</v>
       </c>
       <c r="G1224" t="inlineStr">
         <is>
@@ -31046,22 +31046,22 @@
     </row>
     <row r="1225">
       <c r="A1225" t="n">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B1225" t="n">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="C1225" t="n">
         <v>176</v>
       </c>
       <c r="D1225" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1225" t="n">
-        <v>8.56</v>
+        <v>11.54</v>
       </c>
       <c r="F1225" s="2" t="n">
-        <v>45247.00141032288</v>
+        <v>45247.00210321089</v>
       </c>
       <c r="G1225" t="inlineStr">
         <is>
@@ -31071,22 +31071,22 @@
     </row>
     <row r="1226">
       <c r="A1226" t="n">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B1226" t="n">
-        <v>3055</v>
+        <v>3058</v>
       </c>
       <c r="C1226" t="n">
         <v>176</v>
       </c>
       <c r="D1226" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1226" t="n">
-        <v>11.54</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="F1226" s="2" t="n">
-        <v>45247.00210321089</v>
+        <v>45247.0039468522</v>
       </c>
       <c r="G1226" t="inlineStr">
         <is>
@@ -31096,22 +31096,22 @@
     </row>
     <row r="1227">
       <c r="A1227" t="n">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1227" t="n">
-        <v>3058</v>
+        <v>3061</v>
       </c>
       <c r="C1227" t="n">
         <v>176</v>
       </c>
       <c r="D1227" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1227" t="n">
-        <v>8.609999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="F1227" s="2" t="n">
-        <v>45247.0039468522</v>
+        <v>45247.00617325243</v>
       </c>
       <c r="G1227" t="inlineStr">
         <is>
@@ -31121,22 +31121,22 @@
     </row>
     <row r="1228">
       <c r="A1228" t="n">
-        <v>1693</v>
+        <v>1718</v>
       </c>
       <c r="B1228" t="n">
-        <v>3061</v>
+        <v>3127</v>
       </c>
       <c r="C1228" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D1228" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E1228" t="n">
-        <v>9.6</v>
+        <v>10.12</v>
       </c>
       <c r="F1228" s="2" t="n">
-        <v>45247.00617325243</v>
+        <v>45247.17124424849</v>
       </c>
       <c r="G1228" t="inlineStr">
         <is>
@@ -31146,22 +31146,22 @@
     </row>
     <row r="1229">
       <c r="A1229" t="n">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="B1229" t="n">
-        <v>3127</v>
+        <v>3131</v>
       </c>
       <c r="C1229" t="n">
         <v>181</v>
       </c>
       <c r="D1229" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E1229" t="n">
-        <v>10.12</v>
+        <v>9.92</v>
       </c>
       <c r="F1229" s="2" t="n">
-        <v>45247.17124424849</v>
+        <v>45247.17362783635</v>
       </c>
       <c r="G1229" t="inlineStr">
         <is>
@@ -31171,22 +31171,22 @@
     </row>
     <row r="1230">
       <c r="A1230" t="n">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="B1230" t="n">
-        <v>3131</v>
+        <v>3136</v>
       </c>
       <c r="C1230" t="n">
         <v>181</v>
       </c>
       <c r="D1230" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1230" t="n">
-        <v>9.92</v>
+        <v>19.61</v>
       </c>
       <c r="F1230" s="2" t="n">
-        <v>45247.17362783635</v>
+        <v>45247.1778355942</v>
       </c>
       <c r="G1230" t="inlineStr">
         <is>
@@ -31196,22 +31196,22 @@
     </row>
     <row r="1231">
       <c r="A1231" t="n">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="B1231" t="n">
-        <v>3136</v>
+        <v>3141</v>
       </c>
       <c r="C1231" t="n">
         <v>181</v>
       </c>
       <c r="D1231" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E1231" t="n">
-        <v>19.61</v>
+        <v>8.09</v>
       </c>
       <c r="F1231" s="2" t="n">
-        <v>45247.1778355942</v>
+        <v>45247.18148614821</v>
       </c>
       <c r="G1231" t="inlineStr">
         <is>
@@ -31221,22 +31221,22 @@
     </row>
     <row r="1232">
       <c r="A1232" t="n">
-        <v>1723</v>
+        <v>1279</v>
       </c>
       <c r="B1232" t="n">
-        <v>3141</v>
+        <v>2237</v>
       </c>
       <c r="C1232" t="n">
-        <v>181</v>
+        <v>126</v>
       </c>
       <c r="D1232" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E1232" t="n">
-        <v>8.09</v>
+        <v>9.35</v>
       </c>
       <c r="F1232" s="2" t="n">
-        <v>45247.18148614821</v>
+        <v>45244.17323332567</v>
       </c>
       <c r="G1232" t="inlineStr">
         <is>
@@ -31246,22 +31246,22 @@
     </row>
     <row r="1233">
       <c r="A1233" t="n">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="B1233" t="n">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="C1233" t="n">
         <v>126</v>
       </c>
       <c r="D1233" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E1233" t="n">
-        <v>9.35</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F1233" s="2" t="n">
-        <v>45244.17323332567</v>
+        <v>45244.17652330363</v>
       </c>
       <c r="G1233" t="inlineStr">
         <is>
@@ -31271,22 +31271,22 @@
     </row>
     <row r="1234">
       <c r="A1234" t="n">
-        <v>1282</v>
+        <v>1529</v>
       </c>
       <c r="B1234" t="n">
-        <v>2240</v>
+        <v>2711</v>
       </c>
       <c r="C1234" t="n">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="D1234" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1234" t="n">
-        <v>8.949999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="F1234" s="2" t="n">
-        <v>45244.17652330363</v>
+        <v>45245.19979635652</v>
       </c>
       <c r="G1234" t="inlineStr">
         <is>
@@ -31296,22 +31296,22 @@
     </row>
     <row r="1235">
       <c r="A1235" t="n">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="B1235" t="n">
-        <v>2711</v>
+        <v>2717</v>
       </c>
       <c r="C1235" t="n">
         <v>153</v>
       </c>
       <c r="D1235" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E1235" t="n">
-        <v>9.81</v>
+        <v>11.53</v>
       </c>
       <c r="F1235" s="2" t="n">
-        <v>45245.19979635652</v>
+        <v>45245.2051403589</v>
       </c>
       <c r="G1235" t="inlineStr">
         <is>
@@ -31321,22 +31321,22 @@
     </row>
     <row r="1236">
       <c r="A1236" t="n">
-        <v>1531</v>
+        <v>1535</v>
       </c>
       <c r="B1236" t="n">
-        <v>2717</v>
+        <v>2729</v>
       </c>
       <c r="C1236" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D1236" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E1236" t="n">
-        <v>11.53</v>
+        <v>10.12</v>
       </c>
       <c r="F1236" s="2" t="n">
-        <v>45245.2051403589</v>
+        <v>45245.23541459804</v>
       </c>
       <c r="G1236" t="inlineStr">
         <is>
@@ -31346,22 +31346,22 @@
     </row>
     <row r="1237">
       <c r="A1237" t="n">
-        <v>1535</v>
+        <v>1574</v>
       </c>
       <c r="B1237" t="n">
-        <v>2729</v>
+        <v>2819</v>
       </c>
       <c r="C1237" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D1237" t="n">
         <v>8</v>
       </c>
       <c r="E1237" t="n">
-        <v>10.12</v>
+        <v>11.93</v>
       </c>
       <c r="F1237" s="2" t="n">
-        <v>45245.23541459804</v>
+        <v>45245.97771395952</v>
       </c>
       <c r="G1237" t="inlineStr">
         <is>
@@ -31371,22 +31371,22 @@
     </row>
     <row r="1238">
       <c r="A1238" t="n">
-        <v>1574</v>
+        <v>1602</v>
       </c>
       <c r="B1238" t="n">
-        <v>2819</v>
+        <v>2881</v>
       </c>
       <c r="C1238" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D1238" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1238" t="n">
-        <v>11.93</v>
+        <v>11.14</v>
       </c>
       <c r="F1238" s="2" t="n">
-        <v>45245.97771395952</v>
+        <v>45246.39262756678</v>
       </c>
       <c r="G1238" t="inlineStr">
         <is>
@@ -31396,22 +31396,22 @@
     </row>
     <row r="1239">
       <c r="A1239" t="n">
-        <v>1602</v>
+        <v>1648</v>
       </c>
       <c r="B1239" t="n">
-        <v>2881</v>
+        <v>2967</v>
       </c>
       <c r="C1239" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D1239" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1239" t="n">
-        <v>11.14</v>
+        <v>12.41</v>
       </c>
       <c r="F1239" s="2" t="n">
-        <v>45246.39262756678</v>
+        <v>45246.66282455371</v>
       </c>
       <c r="G1239" t="inlineStr">
         <is>
@@ -31421,22 +31421,22 @@
     </row>
     <row r="1240">
       <c r="A1240" t="n">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B1240" t="n">
-        <v>2967</v>
+        <v>2970</v>
       </c>
       <c r="C1240" t="n">
         <v>170</v>
       </c>
       <c r="D1240" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1240" t="n">
-        <v>12.41</v>
+        <v>10.4</v>
       </c>
       <c r="F1240" s="2" t="n">
-        <v>45246.66282455371</v>
+        <v>45246.66478124687</v>
       </c>
       <c r="G1240" t="inlineStr">
         <is>
@@ -31446,22 +31446,22 @@
     </row>
     <row r="1241">
       <c r="A1241" t="n">
-        <v>1649</v>
+        <v>1668</v>
       </c>
       <c r="B1241" t="n">
-        <v>2970</v>
+        <v>3011</v>
       </c>
       <c r="C1241" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D1241" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1241" t="n">
-        <v>10.4</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="F1241" s="2" t="n">
-        <v>45246.66478124687</v>
+        <v>45246.85797114565</v>
       </c>
       <c r="G1241" t="inlineStr">
         <is>
@@ -31471,22 +31471,22 @@
     </row>
     <row r="1242">
       <c r="A1242" t="n">
-        <v>1668</v>
+        <v>1672</v>
       </c>
       <c r="B1242" t="n">
-        <v>3011</v>
+        <v>3020</v>
       </c>
       <c r="C1242" t="n">
         <v>173</v>
       </c>
       <c r="D1242" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E1242" t="n">
-        <v>9.869999999999999</v>
+        <v>10.87</v>
       </c>
       <c r="F1242" s="2" t="n">
-        <v>45246.85797114565</v>
+        <v>45246.86498953704</v>
       </c>
       <c r="G1242" t="inlineStr">
         <is>
@@ -31496,22 +31496,22 @@
     </row>
     <row r="1243">
       <c r="A1243" t="n">
-        <v>1672</v>
+        <v>1684</v>
       </c>
       <c r="B1243" t="n">
-        <v>3020</v>
+        <v>3042</v>
       </c>
       <c r="C1243" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D1243" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E1243" t="n">
-        <v>10.87</v>
+        <v>8.82</v>
       </c>
       <c r="F1243" s="2" t="n">
-        <v>45246.86498953704</v>
+        <v>45246.92240427351</v>
       </c>
       <c r="G1243" t="inlineStr">
         <is>
@@ -31521,22 +31521,22 @@
     </row>
     <row r="1244">
       <c r="A1244" t="n">
-        <v>1684</v>
+        <v>1646</v>
       </c>
       <c r="B1244" t="n">
-        <v>3042</v>
+        <v>2963</v>
       </c>
       <c r="C1244" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D1244" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E1244" t="n">
-        <v>8.82</v>
+        <v>12.99</v>
       </c>
       <c r="F1244" s="2" t="n">
-        <v>45246.92240427351</v>
+        <v>45246.66071754423</v>
       </c>
       <c r="G1244" t="inlineStr">
         <is>
@@ -31546,22 +31546,22 @@
     </row>
     <row r="1245">
       <c r="A1245" t="n">
-        <v>1646</v>
+        <v>1676</v>
       </c>
       <c r="B1245" t="n">
-        <v>2963</v>
+        <v>3025</v>
       </c>
       <c r="C1245" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D1245" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E1245" t="n">
-        <v>12.99</v>
+        <v>18.01</v>
       </c>
       <c r="F1245" s="2" t="n">
-        <v>45246.66071754423</v>
+        <v>45246.89117958806</v>
       </c>
       <c r="G1245" t="inlineStr">
         <is>
@@ -31571,22 +31571,22 @@
     </row>
     <row r="1246">
       <c r="A1246" t="n">
-        <v>1676</v>
+        <v>1694</v>
       </c>
       <c r="B1246" t="n">
-        <v>3025</v>
+        <v>3064</v>
       </c>
       <c r="C1246" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D1246" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E1246" t="n">
-        <v>18.01</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="F1246" s="2" t="n">
-        <v>45246.89117958806</v>
+        <v>45247.00889589202</v>
       </c>
       <c r="G1246" t="inlineStr">
         <is>
@@ -31596,22 +31596,22 @@
     </row>
     <row r="1247">
       <c r="A1247" t="n">
-        <v>1694</v>
+        <v>1721</v>
       </c>
       <c r="B1247" t="n">
-        <v>3064</v>
+        <v>3132</v>
       </c>
       <c r="C1247" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D1247" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E1247" t="n">
-        <v>8.460000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="F1247" s="2" t="n">
-        <v>45247.00889589202</v>
+        <v>45247.17441298727</v>
       </c>
       <c r="G1247" t="inlineStr">
         <is>
@@ -31621,22 +31621,22 @@
     </row>
     <row r="1248">
       <c r="A1248" t="n">
-        <v>1721</v>
+        <v>1458</v>
       </c>
       <c r="B1248" t="n">
-        <v>3132</v>
+        <v>2552</v>
       </c>
       <c r="C1248" t="n">
-        <v>181</v>
+        <v>143</v>
       </c>
       <c r="D1248" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E1248" t="n">
-        <v>9.49</v>
+        <v>12.6</v>
       </c>
       <c r="F1248" s="2" t="n">
-        <v>45247.17441298727</v>
+        <v>45244.78416309629</v>
       </c>
       <c r="G1248" t="inlineStr">
         <is>
@@ -31646,22 +31646,22 @@
     </row>
     <row r="1249">
       <c r="A1249" t="n">
-        <v>1458</v>
+        <v>1528</v>
       </c>
       <c r="B1249" t="n">
-        <v>2552</v>
+        <v>2707</v>
       </c>
       <c r="C1249" t="n">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D1249" t="n">
         <v>1</v>
       </c>
       <c r="E1249" t="n">
-        <v>12.6</v>
+        <v>10.27</v>
       </c>
       <c r="F1249" s="2" t="n">
-        <v>45244.78416309629</v>
+        <v>45245.19691450314</v>
       </c>
       <c r="G1249" t="inlineStr">
         <is>
@@ -31671,22 +31671,22 @@
     </row>
     <row r="1250">
       <c r="A1250" t="n">
-        <v>1528</v>
+        <v>1532</v>
       </c>
       <c r="B1250" t="n">
-        <v>2707</v>
+        <v>2720</v>
       </c>
       <c r="C1250" t="n">
         <v>153</v>
       </c>
       <c r="D1250" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E1250" t="n">
-        <v>10.27</v>
+        <v>11.09</v>
       </c>
       <c r="F1250" s="2" t="n">
-        <v>45245.19691450314</v>
+        <v>45245.20964881693</v>
       </c>
       <c r="G1250" t="inlineStr">
         <is>
@@ -31696,22 +31696,22 @@
     </row>
     <row r="1251">
       <c r="A1251" t="n">
-        <v>1532</v>
+        <v>1573</v>
       </c>
       <c r="B1251" t="n">
-        <v>2720</v>
+        <v>2817</v>
       </c>
       <c r="C1251" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D1251" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E1251" t="n">
-        <v>11.09</v>
+        <v>30</v>
       </c>
       <c r="F1251" s="2" t="n">
-        <v>45245.20964881693</v>
+        <v>45245.97637159583</v>
       </c>
       <c r="G1251" t="inlineStr">
         <is>
@@ -31721,22 +31721,22 @@
     </row>
     <row r="1252">
       <c r="A1252" t="n">
-        <v>1573</v>
+        <v>1576</v>
       </c>
       <c r="B1252" t="n">
-        <v>2817</v>
+        <v>2823</v>
       </c>
       <c r="C1252" t="n">
         <v>160</v>
       </c>
       <c r="D1252" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E1252" t="n">
         <v>30</v>
       </c>
       <c r="F1252" s="2" t="n">
-        <v>45245.97637159583</v>
+        <v>45245.98137506161</v>
       </c>
       <c r="G1252" t="inlineStr">
         <is>
@@ -31746,22 +31746,22 @@
     </row>
     <row r="1253">
       <c r="A1253" t="n">
-        <v>1576</v>
+        <v>1600</v>
       </c>
       <c r="B1253" t="n">
-        <v>2823</v>
+        <v>2877</v>
       </c>
       <c r="C1253" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D1253" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E1253" t="n">
-        <v>30</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F1253" s="2" t="n">
-        <v>45245.98137506161</v>
+        <v>45246.38916890263</v>
       </c>
       <c r="G1253" t="inlineStr">
         <is>
@@ -31771,22 +31771,22 @@
     </row>
     <row r="1254">
       <c r="A1254" t="n">
-        <v>1600</v>
+        <v>1657</v>
       </c>
       <c r="B1254" t="n">
-        <v>2877</v>
+        <v>2985</v>
       </c>
       <c r="C1254" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D1254" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1254" t="n">
-        <v>8.949999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="F1254" s="2" t="n">
-        <v>45246.38916890263</v>
+        <v>45246.75125015287</v>
       </c>
       <c r="G1254" t="inlineStr">
         <is>
@@ -31796,22 +31796,22 @@
     </row>
     <row r="1255">
       <c r="A1255" t="n">
-        <v>1657</v>
+        <v>1675</v>
       </c>
       <c r="B1255" t="n">
-        <v>2985</v>
+        <v>3024</v>
       </c>
       <c r="C1255" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D1255" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1255" t="n">
-        <v>9.220000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F1255" s="2" t="n">
-        <v>45246.75125015287</v>
+        <v>45246.89026023034</v>
       </c>
       <c r="G1255" t="inlineStr">
         <is>
@@ -31821,22 +31821,22 @@
     </row>
     <row r="1256">
       <c r="A1256" t="n">
-        <v>1675</v>
+        <v>1655</v>
       </c>
       <c r="B1256" t="n">
-        <v>3024</v>
+        <v>2982</v>
       </c>
       <c r="C1256" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D1256" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E1256" t="n">
-        <v>9.140000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="F1256" s="2" t="n">
-        <v>45246.89026023034</v>
+        <v>45246.74937147988</v>
       </c>
       <c r="G1256" t="inlineStr">
         <is>
@@ -31846,22 +31846,22 @@
     </row>
     <row r="1257">
       <c r="A1257" t="n">
-        <v>1655</v>
+        <v>1677</v>
       </c>
       <c r="B1257" t="n">
-        <v>2982</v>
+        <v>3027</v>
       </c>
       <c r="C1257" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D1257" t="n">
         <v>6</v>
       </c>
       <c r="E1257" t="n">
-        <v>9.33</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="F1257" s="2" t="n">
-        <v>45246.74937147988</v>
+        <v>45246.89221943357</v>
       </c>
       <c r="G1257" t="inlineStr">
         <is>
@@ -31871,22 +31871,22 @@
     </row>
     <row r="1258">
       <c r="A1258" t="n">
-        <v>1677</v>
+        <v>1181</v>
       </c>
       <c r="B1258" t="n">
-        <v>3027</v>
+        <v>2064</v>
       </c>
       <c r="C1258" t="n">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="D1258" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E1258" t="n">
-        <v>9.220000000000001</v>
+        <v>10.93</v>
       </c>
       <c r="F1258" s="2" t="n">
-        <v>45246.89221943357</v>
+        <v>45243.7693660345</v>
       </c>
       <c r="G1258" t="inlineStr">
         <is>
@@ -31896,22 +31896,22 @@
     </row>
     <row r="1259">
       <c r="A1259" t="n">
-        <v>1181</v>
+        <v>1417</v>
       </c>
       <c r="B1259" t="n">
-        <v>2064</v>
+        <v>2467</v>
       </c>
       <c r="C1259" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="D1259" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E1259" t="n">
-        <v>10.93</v>
+        <v>10.22</v>
       </c>
       <c r="F1259" s="2" t="n">
-        <v>45243.7693660345</v>
+        <v>45244.53226980544</v>
       </c>
       <c r="G1259" t="inlineStr">
         <is>
@@ -31921,22 +31921,22 @@
     </row>
     <row r="1260">
       <c r="A1260" t="n">
-        <v>1417</v>
+        <v>1670</v>
       </c>
       <c r="B1260" t="n">
-        <v>2467</v>
+        <v>3015</v>
       </c>
       <c r="C1260" t="n">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="D1260" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E1260" t="n">
         <v>10.22</v>
       </c>
       <c r="F1260" s="2" t="n">
-        <v>45244.53226980544</v>
+        <v>45246.86099143763</v>
       </c>
       <c r="G1260" t="inlineStr">
         <is>
@@ -31946,22 +31946,22 @@
     </row>
     <row r="1261">
       <c r="A1261" t="n">
-        <v>1670</v>
+        <v>1686</v>
       </c>
       <c r="B1261" t="n">
-        <v>3015</v>
+        <v>3046</v>
       </c>
       <c r="C1261" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D1261" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1261" t="n">
-        <v>10.22</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F1261" s="2" t="n">
-        <v>45246.86099143763</v>
+        <v>45246.92514060332</v>
       </c>
       <c r="G1261" t="inlineStr">
         <is>
@@ -31971,22 +31971,22 @@
     </row>
     <row r="1262">
       <c r="A1262" t="n">
-        <v>1686</v>
+        <v>1176</v>
       </c>
       <c r="B1262" t="n">
-        <v>3046</v>
+        <v>2057</v>
       </c>
       <c r="C1262" t="n">
-        <v>175</v>
+        <v>114</v>
       </c>
       <c r="D1262" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1262" t="n">
-        <v>8.949999999999999</v>
+        <v>13.74</v>
       </c>
       <c r="F1262" s="2" t="n">
-        <v>45246.92514060332</v>
+        <v>45243.76391041237</v>
       </c>
       <c r="G1262" t="inlineStr">
         <is>
@@ -31996,22 +31996,22 @@
     </row>
     <row r="1263">
       <c r="A1263" t="n">
-        <v>1176</v>
+        <v>1719</v>
       </c>
       <c r="B1263" t="n">
-        <v>2057</v>
+        <v>3128</v>
       </c>
       <c r="C1263" t="n">
-        <v>114</v>
+        <v>181</v>
       </c>
       <c r="D1263" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E1263" t="n">
-        <v>13.74</v>
+        <v>19.18</v>
       </c>
       <c r="F1263" s="2" t="n">
-        <v>45243.76391041237</v>
+        <v>45247.17200462607</v>
       </c>
       <c r="G1263" t="inlineStr">
         <is>
@@ -32021,22 +32021,22 @@
     </row>
     <row r="1264">
       <c r="A1264" t="n">
-        <v>1719</v>
+        <v>1575</v>
       </c>
       <c r="B1264" t="n">
-        <v>3128</v>
+        <v>2821</v>
       </c>
       <c r="C1264" t="n">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="D1264" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E1264" t="n">
-        <v>19.18</v>
+        <v>10.48</v>
       </c>
       <c r="F1264" s="2" t="n">
-        <v>45247.17200462607</v>
+        <v>45245.97967322704</v>
       </c>
       <c r="G1264" t="inlineStr">
         <is>
@@ -32046,47 +32046,47 @@
     </row>
     <row r="1265">
       <c r="A1265" t="n">
-        <v>1575</v>
+        <v>1172</v>
       </c>
       <c r="B1265" t="n">
-        <v>2821</v>
+        <v>2051</v>
       </c>
       <c r="C1265" t="n">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="D1265" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1265" t="n">
-        <v>10.48</v>
+        <v>12.768967</v>
       </c>
       <c r="F1265" s="2" t="n">
-        <v>45245.97967322704</v>
+        <v>45243.75685873781</v>
       </c>
       <c r="G1265" t="inlineStr">
         <is>
-          <t>Corrected: ResponseTime</t>
+          <t>Original: not a correction</t>
         </is>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="n">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B1266" t="n">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="C1266" t="n">
         <v>114</v>
       </c>
       <c r="D1266" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1266" t="n">
-        <v>12.768967</v>
+        <v>23.18238</v>
       </c>
       <c r="F1266" s="2" t="n">
-        <v>45243.75685873781</v>
+        <v>45243.7578837141</v>
       </c>
       <c r="G1266" t="inlineStr">
         <is>
@@ -32096,22 +32096,22 @@
     </row>
     <row r="1267">
       <c r="A1267" t="n">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B1267" t="n">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="C1267" t="n">
         <v>114</v>
       </c>
       <c r="D1267" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1267" t="n">
-        <v>23.18238</v>
+        <v>10.332961</v>
       </c>
       <c r="F1267" s="2" t="n">
-        <v>45243.7578837141</v>
+        <v>45243.75833139644</v>
       </c>
       <c r="G1267" t="inlineStr">
         <is>
@@ -32121,22 +32121,22 @@
     </row>
     <row r="1268">
       <c r="A1268" t="n">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="B1268" t="n">
-        <v>2053</v>
+        <v>2066</v>
       </c>
       <c r="C1268" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D1268" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E1268" t="n">
-        <v>10.332961</v>
+        <v>11.548277</v>
       </c>
       <c r="F1268" s="2" t="n">
-        <v>45243.75833139644</v>
+        <v>45243.81754935643</v>
       </c>
       <c r="G1268" t="inlineStr">
         <is>
@@ -32146,22 +32146,22 @@
     </row>
     <row r="1269">
       <c r="A1269" t="n">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B1269" t="n">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="C1269" t="n">
         <v>115</v>
       </c>
       <c r="D1269" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1269" t="n">
-        <v>11.548277</v>
+        <v>25.933465</v>
       </c>
       <c r="F1269" s="2" t="n">
-        <v>45243.81754935643</v>
+        <v>45243.81859577195</v>
       </c>
       <c r="G1269" t="inlineStr">
         <is>
@@ -32171,22 +32171,22 @@
     </row>
     <row r="1270">
       <c r="A1270" t="n">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="B1270" t="n">
-        <v>2067</v>
+        <v>2071</v>
       </c>
       <c r="C1270" t="n">
         <v>115</v>
       </c>
       <c r="D1270" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E1270" t="n">
-        <v>25.933465</v>
+        <v>13.894136</v>
       </c>
       <c r="F1270" s="2" t="n">
-        <v>45243.81859577195</v>
+        <v>45243.82124813415</v>
       </c>
       <c r="G1270" t="inlineStr">
         <is>
@@ -32196,22 +32196,22 @@
     </row>
     <row r="1271">
       <c r="A1271" t="n">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B1271" t="n">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="C1271" t="n">
         <v>115</v>
       </c>
       <c r="D1271" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1271" t="n">
-        <v>13.894136</v>
+        <v>12.609812</v>
       </c>
       <c r="F1271" s="2" t="n">
-        <v>45243.82124813415</v>
+        <v>45243.82293784311</v>
       </c>
       <c r="G1271" t="inlineStr">
         <is>
@@ -32221,22 +32221,22 @@
     </row>
     <row r="1272">
       <c r="A1272" t="n">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B1272" t="n">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="C1272" t="n">
         <v>115</v>
       </c>
       <c r="D1272" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1272" t="n">
-        <v>12.609812</v>
+        <v>13.498791</v>
       </c>
       <c r="F1272" s="2" t="n">
-        <v>45243.82293784311</v>
+        <v>45243.82407331125</v>
       </c>
       <c r="G1272" t="inlineStr">
         <is>
@@ -32246,22 +32246,22 @@
     </row>
     <row r="1273">
       <c r="A1273" t="n">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="B1273" t="n">
-        <v>2074</v>
+        <v>2081</v>
       </c>
       <c r="C1273" t="n">
         <v>115</v>
       </c>
       <c r="D1273" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E1273" t="n">
-        <v>13.498791</v>
+        <v>10.261263</v>
       </c>
       <c r="F1273" s="2" t="n">
-        <v>45243.82407331125</v>
+        <v>45243.82948400684</v>
       </c>
       <c r="G1273" t="inlineStr">
         <is>
@@ -32271,22 +32271,22 @@
     </row>
     <row r="1274">
       <c r="A1274" t="n">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="B1274" t="n">
-        <v>2081</v>
+        <v>2084</v>
       </c>
       <c r="C1274" t="n">
         <v>115</v>
       </c>
       <c r="D1274" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1274" t="n">
-        <v>10.261263</v>
+        <v>16.025671</v>
       </c>
       <c r="F1274" s="2" t="n">
-        <v>45243.82948400684</v>
+        <v>45243.83224600435</v>
       </c>
       <c r="G1274" t="inlineStr">
         <is>
@@ -32296,22 +32296,22 @@
     </row>
     <row r="1275">
       <c r="A1275" t="n">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B1275" t="n">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="C1275" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D1275" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E1275" t="n">
-        <v>16.025671</v>
+        <v>13.742066</v>
       </c>
       <c r="F1275" s="2" t="n">
-        <v>45243.83224600435</v>
+        <v>45243.86968914399</v>
       </c>
       <c r="G1275" t="inlineStr">
         <is>
@@ -32321,22 +32321,22 @@
     </row>
     <row r="1276">
       <c r="A1276" t="n">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B1276" t="n">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="C1276" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D1276" t="n">
         <v>1</v>
       </c>
       <c r="E1276" t="n">
-        <v>13.742066</v>
+        <v>2.020088</v>
       </c>
       <c r="F1276" s="2" t="n">
-        <v>45243.86968914399</v>
+        <v>45243.8714851263</v>
       </c>
       <c r="G1276" t="inlineStr">
         <is>
@@ -32346,22 +32346,22 @@
     </row>
     <row r="1277">
       <c r="A1277" t="n">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B1277" t="n">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="C1277" t="n">
         <v>117</v>
       </c>
       <c r="D1277" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1277" t="n">
-        <v>2.020088</v>
+        <v>16.310504</v>
       </c>
       <c r="F1277" s="2" t="n">
-        <v>45243.8714851263</v>
+        <v>45243.8725473303</v>
       </c>
       <c r="G1277" t="inlineStr">
         <is>
@@ -32371,22 +32371,22 @@
     </row>
     <row r="1278">
       <c r="A1278" t="n">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B1278" t="n">
-        <v>2090</v>
+        <v>2093</v>
       </c>
       <c r="C1278" t="n">
         <v>117</v>
       </c>
       <c r="D1278" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E1278" t="n">
-        <v>16.310504</v>
+        <v>23.194248</v>
       </c>
       <c r="F1278" s="2" t="n">
-        <v>45243.8725473303</v>
+        <v>45243.87524838487</v>
       </c>
       <c r="G1278" t="inlineStr">
         <is>
@@ -32396,22 +32396,22 @@
     </row>
     <row r="1279">
       <c r="A1279" t="n">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B1279" t="n">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="C1279" t="n">
         <v>117</v>
       </c>
       <c r="D1279" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1279" t="n">
-        <v>23.194248</v>
+        <v>13.325223</v>
       </c>
       <c r="F1279" s="2" t="n">
-        <v>45243.87524838487</v>
+        <v>45243.87721321844</v>
       </c>
       <c r="G1279" t="inlineStr">
         <is>
@@ -32421,22 +32421,22 @@
     </row>
     <row r="1280">
       <c r="A1280" t="n">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="B1280" t="n">
-        <v>2095</v>
+        <v>2098</v>
       </c>
       <c r="C1280" t="n">
         <v>117</v>
       </c>
       <c r="D1280" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E1280" t="n">
-        <v>13.325223</v>
+        <v>14.998147</v>
       </c>
       <c r="F1280" s="2" t="n">
-        <v>45243.87721321844</v>
+        <v>45243.880168724</v>
       </c>
       <c r="G1280" t="inlineStr">
         <is>
@@ -32446,22 +32446,22 @@
     </row>
     <row r="1281">
       <c r="A1281" t="n">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="B1281" t="n">
-        <v>2098</v>
+        <v>2101</v>
       </c>
       <c r="C1281" t="n">
         <v>117</v>
       </c>
       <c r="D1281" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1281" t="n">
-        <v>14.998147</v>
+        <v>11.103353</v>
       </c>
       <c r="F1281" s="2" t="n">
-        <v>45243.880168724</v>
+        <v>45243.88265741357</v>
       </c>
       <c r="G1281" t="inlineStr">
         <is>
@@ -32471,22 +32471,22 @@
     </row>
     <row r="1282">
       <c r="A1282" t="n">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B1282" t="n">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="C1282" t="n">
         <v>117</v>
       </c>
       <c r="D1282" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1282" t="n">
-        <v>11.103353</v>
+        <v>15.989814</v>
       </c>
       <c r="F1282" s="2" t="n">
-        <v>45243.88265741357</v>
+        <v>45243.88530174275</v>
       </c>
       <c r="G1282" t="inlineStr">
         <is>
@@ -32496,22 +32496,22 @@
     </row>
     <row r="1283">
       <c r="A1283" t="n">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B1283" t="n">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="C1283" t="n">
         <v>117</v>
       </c>
       <c r="D1283" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1283" t="n">
-        <v>15.989814</v>
+        <v>14.330217</v>
       </c>
       <c r="F1283" s="2" t="n">
-        <v>45243.88530174275</v>
+        <v>45243.88629079088</v>
       </c>
       <c r="G1283" t="inlineStr">
         <is>
@@ -32521,22 +32521,22 @@
     </row>
     <row r="1284">
       <c r="A1284" t="n">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B1284" t="n">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="C1284" t="n">
         <v>117</v>
       </c>
       <c r="D1284" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1284" t="n">
-        <v>14.330217</v>
+        <v>16.411274</v>
       </c>
       <c r="F1284" s="2" t="n">
-        <v>45243.88629079088</v>
+        <v>45243.88804340529</v>
       </c>
       <c r="G1284" t="inlineStr">
         <is>
@@ -32546,22 +32546,22 @@
     </row>
     <row r="1285">
       <c r="A1285" t="n">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B1285" t="n">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="C1285" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D1285" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E1285" t="n">
-        <v>16.411274</v>
+        <v>12.140508</v>
       </c>
       <c r="F1285" s="2" t="n">
-        <v>45243.88804340529</v>
+        <v>45243.90285049169</v>
       </c>
       <c r="G1285" t="inlineStr">
         <is>
@@ -32571,22 +32571,22 @@
     </row>
     <row r="1286">
       <c r="A1286" t="n">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B1286" t="n">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="C1286" t="n">
         <v>118</v>
       </c>
       <c r="D1286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1286" t="n">
-        <v>12.140508</v>
+        <v>10.617271</v>
       </c>
       <c r="F1286" s="2" t="n">
-        <v>45243.90285049169</v>
+        <v>45243.90375138406</v>
       </c>
       <c r="G1286" t="inlineStr">
         <is>
@@ -32596,22 +32596,22 @@
     </row>
     <row r="1287">
       <c r="A1287" t="n">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B1287" t="n">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="C1287" t="n">
         <v>118</v>
       </c>
       <c r="D1287" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1287" t="n">
-        <v>10.617271</v>
+        <v>11.344383</v>
       </c>
       <c r="F1287" s="2" t="n">
-        <v>45243.90375138406</v>
+        <v>45243.90469877987</v>
       </c>
       <c r="G1287" t="inlineStr">
         <is>
@@ -32621,22 +32621,22 @@
     </row>
     <row r="1288">
       <c r="A1288" t="n">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B1288" t="n">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="C1288" t="n">
         <v>118</v>
       </c>
       <c r="D1288" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1288" t="n">
-        <v>11.344383</v>
+        <v>12.48606</v>
       </c>
       <c r="F1288" s="2" t="n">
-        <v>45243.90469877987</v>
+        <v>45243.90560876857</v>
       </c>
       <c r="G1288" t="inlineStr">
         <is>
@@ -32646,22 +32646,22 @@
     </row>
     <row r="1289">
       <c r="A1289" t="n">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B1289" t="n">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="C1289" t="n">
         <v>118</v>
       </c>
       <c r="D1289" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1289" t="n">
-        <v>12.48606</v>
+        <v>11.486967</v>
       </c>
       <c r="F1289" s="2" t="n">
-        <v>45243.90560876857</v>
+        <v>45243.90634991792</v>
       </c>
       <c r="G1289" t="inlineStr">
         <is>
@@ -32671,22 +32671,22 @@
     </row>
     <row r="1290">
       <c r="A1290" t="n">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B1290" t="n">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1290" t="n">
         <v>118</v>
       </c>
       <c r="D1290" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1290" t="n">
-        <v>11.486967</v>
+        <v>11.970624</v>
       </c>
       <c r="F1290" s="2" t="n">
-        <v>45243.90634991792</v>
+        <v>45243.90711752817</v>
       </c>
       <c r="G1290" t="inlineStr">
         <is>
@@ -32696,22 +32696,22 @@
     </row>
     <row r="1291">
       <c r="A1291" t="n">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="B1291" t="n">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="C1291" t="n">
         <v>118</v>
       </c>
       <c r="D1291" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1291" t="n">
-        <v>11.970624</v>
+        <v>12.994309</v>
       </c>
       <c r="F1291" s="2" t="n">
-        <v>45243.90711752817</v>
+        <v>45243.90900882612</v>
       </c>
       <c r="G1291" t="inlineStr">
         <is>
@@ -32721,22 +32721,22 @@
     </row>
     <row r="1292">
       <c r="A1292" t="n">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B1292" t="n">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="C1292" t="n">
         <v>118</v>
       </c>
       <c r="D1292" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1292" t="n">
-        <v>12.994309</v>
+        <v>12.224055</v>
       </c>
       <c r="F1292" s="2" t="n">
-        <v>45243.90900882612</v>
+        <v>45243.90987858569</v>
       </c>
       <c r="G1292" t="inlineStr">
         <is>
@@ -32746,22 +32746,22 @@
     </row>
     <row r="1293">
       <c r="A1293" t="n">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B1293" t="n">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="C1293" t="n">
         <v>118</v>
       </c>
       <c r="D1293" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1293" t="n">
-        <v>12.224055</v>
+        <v>11.995294</v>
       </c>
       <c r="F1293" s="2" t="n">
-        <v>45243.90987858569</v>
+        <v>45243.91070384208</v>
       </c>
       <c r="G1293" t="inlineStr">
         <is>
@@ -32771,22 +32771,22 @@
     </row>
     <row r="1294">
       <c r="A1294" t="n">
-        <v>1214</v>
+        <v>1226</v>
       </c>
       <c r="B1294" t="n">
-        <v>2117</v>
+        <v>2148</v>
       </c>
       <c r="C1294" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D1294" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E1294" t="n">
-        <v>11.995294</v>
+        <v>14.736471</v>
       </c>
       <c r="F1294" s="2" t="n">
-        <v>45243.91070384208</v>
+        <v>45243.98292481603</v>
       </c>
       <c r="G1294" t="inlineStr">
         <is>
@@ -32796,22 +32796,22 @@
     </row>
     <row r="1295">
       <c r="A1295" t="n">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B1295" t="n">
-        <v>2148</v>
+        <v>2154</v>
       </c>
       <c r="C1295" t="n">
         <v>120</v>
       </c>
       <c r="D1295" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E1295" t="n">
-        <v>14.736471</v>
+        <v>29.157159</v>
       </c>
       <c r="F1295" s="2" t="n">
-        <v>45243.98292481603</v>
+        <v>45243.98907675187</v>
       </c>
       <c r="G1295" t="inlineStr">
         <is>
@@ -32821,22 +32821,22 @@
     </row>
     <row r="1296">
       <c r="A1296" t="n">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="B1296" t="n">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="C1296" t="n">
         <v>120</v>
       </c>
       <c r="D1296" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1296" t="n">
-        <v>29.157159</v>
+        <v>15.240089</v>
       </c>
       <c r="F1296" s="2" t="n">
-        <v>45243.98907675187</v>
+        <v>45243.99082257327</v>
       </c>
       <c r="G1296" t="inlineStr">
         <is>
@@ -32846,22 +32846,22 @@
     </row>
     <row r="1297">
       <c r="A1297" t="n">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B1297" t="n">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="C1297" t="n">
         <v>120</v>
       </c>
       <c r="D1297" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1297" t="n">
-        <v>15.240089</v>
+        <v>14.247646</v>
       </c>
       <c r="F1297" s="2" t="n">
-        <v>45243.99082257327</v>
+        <v>45243.99275847265</v>
       </c>
       <c r="G1297" t="inlineStr">
         <is>
@@ -32871,22 +32871,22 @@
     </row>
     <row r="1298">
       <c r="A1298" t="n">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="B1298" t="n">
-        <v>2158</v>
+        <v>2161</v>
       </c>
       <c r="C1298" t="n">
         <v>120</v>
       </c>
       <c r="D1298" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1298" t="n">
-        <v>14.247646</v>
+        <v>20.461648</v>
       </c>
       <c r="F1298" s="2" t="n">
-        <v>45243.99275847265</v>
+        <v>45243.99555695806</v>
       </c>
       <c r="G1298" t="inlineStr">
         <is>
@@ -32896,22 +32896,22 @@
     </row>
     <row r="1299">
       <c r="A1299" t="n">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B1299" t="n">
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="C1299" t="n">
         <v>120</v>
       </c>
       <c r="D1299" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1299" t="n">
-        <v>20.461648</v>
+        <v>12.834829</v>
       </c>
       <c r="F1299" s="2" t="n">
-        <v>45243.99555695806</v>
+        <v>45243.99759951385</v>
       </c>
       <c r="G1299" t="inlineStr">
         <is>
@@ -32921,22 +32921,22 @@
     </row>
     <row r="1300">
       <c r="A1300" t="n">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B1300" t="n">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="C1300" t="n">
         <v>120</v>
       </c>
       <c r="D1300" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1300" t="n">
-        <v>12.834829</v>
+        <v>14.887395</v>
       </c>
       <c r="F1300" s="2" t="n">
-        <v>45243.99759951385</v>
+        <v>45243.99903229828</v>
       </c>
       <c r="G1300" t="inlineStr">
         <is>
@@ -32946,22 +32946,22 @@
     </row>
     <row r="1301">
       <c r="A1301" t="n">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B1301" t="n">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="C1301" t="n">
         <v>120</v>
       </c>
       <c r="D1301" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1301" t="n">
-        <v>14.887395</v>
+        <v>13.976034</v>
       </c>
       <c r="F1301" s="2" t="n">
-        <v>45243.99903229828</v>
+        <v>45244.00103146604</v>
       </c>
       <c r="G1301" t="inlineStr">
         <is>
@@ -32971,22 +32971,22 @@
     </row>
     <row r="1302">
       <c r="A1302" t="n">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="B1302" t="n">
-        <v>2166</v>
+        <v>2172</v>
       </c>
       <c r="C1302" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D1302" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E1302" t="n">
-        <v>13.976034</v>
+        <v>18.098934</v>
       </c>
       <c r="F1302" s="2" t="n">
-        <v>45244.00103146604</v>
+        <v>45244.02186428189</v>
       </c>
       <c r="G1302" t="inlineStr">
         <is>
@@ -32996,22 +32996,22 @@
     </row>
     <row r="1303">
       <c r="A1303" t="n">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B1303" t="n">
-        <v>2172</v>
+        <v>2179</v>
       </c>
       <c r="C1303" t="n">
         <v>121</v>
       </c>
       <c r="D1303" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E1303" t="n">
-        <v>18.098934</v>
+        <v>14.888639</v>
       </c>
       <c r="F1303" s="2" t="n">
-        <v>45244.02186428189</v>
+        <v>45244.02719964681</v>
       </c>
       <c r="G1303" t="inlineStr">
         <is>
@@ -33021,22 +33021,22 @@
     </row>
     <row r="1304">
       <c r="A1304" t="n">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B1304" t="n">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="C1304" t="n">
         <v>121</v>
       </c>
       <c r="D1304" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1304" t="n">
-        <v>14.888639</v>
+        <v>14.47948</v>
       </c>
       <c r="F1304" s="2" t="n">
-        <v>45244.02719964681</v>
+        <v>45244.02886470415</v>
       </c>
       <c r="G1304" t="inlineStr">
         <is>
@@ -33046,22 +33046,22 @@
     </row>
     <row r="1305">
       <c r="A1305" t="n">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B1305" t="n">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="C1305" t="n">
         <v>121</v>
       </c>
       <c r="D1305" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1305" t="n">
-        <v>14.47948</v>
+        <v>16.334112</v>
       </c>
       <c r="F1305" s="2" t="n">
-        <v>45244.02886470415</v>
+        <v>45244.02992820407</v>
       </c>
       <c r="G1305" t="inlineStr">
         <is>
@@ -33071,22 +33071,22 @@
     </row>
     <row r="1306">
       <c r="A1306" t="n">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B1306" t="n">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="C1306" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D1306" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E1306" t="n">
-        <v>16.334112</v>
+        <v>12.120842</v>
       </c>
       <c r="F1306" s="2" t="n">
-        <v>45244.02992820407</v>
+        <v>45244.03768635984</v>
       </c>
       <c r="G1306" t="inlineStr">
         <is>
@@ -33096,22 +33096,22 @@
     </row>
     <row r="1307">
       <c r="A1307" t="n">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="B1307" t="n">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="C1307" t="n">
         <v>122</v>
       </c>
       <c r="D1307" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1307" t="n">
-        <v>12.120842</v>
+        <v>16.448012</v>
       </c>
       <c r="F1307" s="2" t="n">
-        <v>45244.03768635984</v>
+        <v>45244.03985196991</v>
       </c>
       <c r="G1307" t="inlineStr">
         <is>
@@ -33121,22 +33121,22 @@
     </row>
     <row r="1308">
       <c r="A1308" t="n">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B1308" t="n">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="C1308" t="n">
         <v>122</v>
       </c>
       <c r="D1308" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1308" t="n">
-        <v>16.448012</v>
+        <v>12.214549</v>
       </c>
       <c r="F1308" s="2" t="n">
-        <v>45244.03985196991</v>
+        <v>45244.04030925644</v>
       </c>
       <c r="G1308" t="inlineStr">
         <is>
@@ -33146,22 +33146,22 @@
     </row>
     <row r="1309">
       <c r="A1309" t="n">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B1309" t="n">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="C1309" t="n">
         <v>122</v>
       </c>
       <c r="D1309" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1309" t="n">
-        <v>12.214549</v>
+        <v>18.643607</v>
       </c>
       <c r="F1309" s="2" t="n">
-        <v>45244.04030925644</v>
+        <v>45244.04165306083</v>
       </c>
       <c r="G1309" t="inlineStr">
         <is>
@@ -33171,22 +33171,22 @@
     </row>
     <row r="1310">
       <c r="A1310" t="n">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B1310" t="n">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="C1310" t="n">
         <v>122</v>
       </c>
       <c r="D1310" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1310" t="n">
-        <v>18.643607</v>
+        <v>16.178674</v>
       </c>
       <c r="F1310" s="2" t="n">
-        <v>45244.04165306083</v>
+        <v>45244.04211206186</v>
       </c>
       <c r="G1310" t="inlineStr">
         <is>
@@ -33196,22 +33196,22 @@
     </row>
     <row r="1311">
       <c r="A1311" t="n">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B1311" t="n">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="C1311" t="n">
         <v>122</v>
       </c>
       <c r="D1311" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1311" t="n">
-        <v>16.178674</v>
+        <v>11.767239</v>
       </c>
       <c r="F1311" s="2" t="n">
-        <v>45244.04211206186</v>
+        <v>45244.0426245471</v>
       </c>
       <c r="G1311" t="inlineStr">
         <is>
@@ -33221,22 +33221,22 @@
     </row>
     <row r="1312">
       <c r="A1312" t="n">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B1312" t="n">
-        <v>2189</v>
+        <v>2191</v>
       </c>
       <c r="C1312" t="n">
         <v>122</v>
       </c>
       <c r="D1312" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1312" t="n">
-        <v>11.767239</v>
+        <v>11.353419</v>
       </c>
       <c r="F1312" s="2" t="n">
-        <v>45244.0426245471</v>
+        <v>45244.04476087246</v>
       </c>
       <c r="G1312" t="inlineStr">
         <is>
@@ -33246,22 +33246,22 @@
     </row>
     <row r="1313">
       <c r="A1313" t="n">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B1313" t="n">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="C1313" t="n">
         <v>122</v>
       </c>
       <c r="D1313" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1313" t="n">
-        <v>11.353419</v>
+        <v>18.704145</v>
       </c>
       <c r="F1313" s="2" t="n">
-        <v>45244.04476087246</v>
+        <v>45244.04586786006</v>
       </c>
       <c r="G1313" t="inlineStr">
         <is>
@@ -33271,22 +33271,22 @@
     </row>
     <row r="1314">
       <c r="A1314" t="n">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="B1314" t="n">
-        <v>2192</v>
+        <v>2196</v>
       </c>
       <c r="C1314" t="n">
         <v>122</v>
       </c>
       <c r="D1314" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E1314" t="n">
-        <v>18.704145</v>
+        <v>13.929356</v>
       </c>
       <c r="F1314" s="2" t="n">
-        <v>45244.04586786006</v>
+        <v>45244.04938711301</v>
       </c>
       <c r="G1314" t="inlineStr">
         <is>
@@ -33296,22 +33296,22 @@
     </row>
     <row r="1315">
       <c r="A1315" t="n">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B1315" t="n">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="C1315" t="n">
         <v>122</v>
       </c>
       <c r="D1315" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1315" t="n">
-        <v>13.929356</v>
+        <v>11.697164</v>
       </c>
       <c r="F1315" s="2" t="n">
-        <v>45244.04938711301</v>
+        <v>45244.05136450428</v>
       </c>
       <c r="G1315" t="inlineStr">
         <is>
@@ -33321,22 +33321,22 @@
     </row>
     <row r="1316">
       <c r="A1316" t="n">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="B1316" t="n">
-        <v>2198</v>
+        <v>2202</v>
       </c>
       <c r="C1316" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D1316" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E1316" t="n">
-        <v>11.697164</v>
+        <v>13.001098</v>
       </c>
       <c r="F1316" s="2" t="n">
-        <v>45244.05136450428</v>
+        <v>45244.08377256327</v>
       </c>
       <c r="G1316" t="inlineStr">
         <is>
@@ -33346,22 +33346,22 @@
     </row>
     <row r="1317">
       <c r="A1317" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="B1317" t="n">
-        <v>2202</v>
+        <v>2205</v>
       </c>
       <c r="C1317" t="n">
         <v>124</v>
       </c>
       <c r="D1317" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E1317" t="n">
-        <v>13.001098</v>
+        <v>11.989361</v>
       </c>
       <c r="F1317" s="2" t="n">
-        <v>45244.08377256327</v>
+        <v>45244.08550067044</v>
       </c>
       <c r="G1317" t="inlineStr">
         <is>
@@ -33371,22 +33371,22 @@
     </row>
     <row r="1318">
       <c r="A1318" t="n">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B1318" t="n">
-        <v>2205</v>
+        <v>2208</v>
       </c>
       <c r="C1318" t="n">
         <v>124</v>
       </c>
       <c r="D1318" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1318" t="n">
-        <v>11.989361</v>
+        <v>20.507462</v>
       </c>
       <c r="F1318" s="2" t="n">
-        <v>45244.08550067044</v>
+        <v>45244.08764556712</v>
       </c>
       <c r="G1318" t="inlineStr">
         <is>
@@ -33396,22 +33396,22 @@
     </row>
     <row r="1319">
       <c r="A1319" t="n">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B1319" t="n">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="C1319" t="n">
         <v>124</v>
       </c>
       <c r="D1319" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1319" t="n">
-        <v>20.507462</v>
+        <v>12.372349</v>
       </c>
       <c r="F1319" s="2" t="n">
-        <v>45244.08764556712</v>
+        <v>45244.08813924448</v>
       </c>
       <c r="G1319" t="inlineStr">
         <is>
@@ -33421,22 +33421,22 @@
     </row>
     <row r="1320">
       <c r="A1320" t="n">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B1320" t="n">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="C1320" t="n">
         <v>124</v>
       </c>
       <c r="D1320" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1320" t="n">
-        <v>12.372349</v>
+        <v>12.729014</v>
       </c>
       <c r="F1320" s="2" t="n">
-        <v>45244.08813924448</v>
+        <v>45244.08873619829</v>
       </c>
       <c r="G1320" t="inlineStr">
         <is>
@@ -33446,22 +33446,22 @@
     </row>
     <row r="1321">
       <c r="A1321" t="n">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B1321" t="n">
-        <v>2210</v>
+        <v>2212</v>
       </c>
       <c r="C1321" t="n">
         <v>124</v>
       </c>
       <c r="D1321" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1321" t="n">
-        <v>12.729014</v>
+        <v>12.699451</v>
       </c>
       <c r="F1321" s="2" t="n">
-        <v>45244.08873619829</v>
+        <v>45244.09005195486</v>
       </c>
       <c r="G1321" t="inlineStr">
         <is>
@@ -33471,22 +33471,22 @@
     </row>
     <row r="1322">
       <c r="A1322" t="n">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B1322" t="n">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="C1322" t="n">
         <v>124</v>
       </c>
       <c r="D1322" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1322" t="n">
-        <v>12.699451</v>
+        <v>20.890063</v>
       </c>
       <c r="F1322" s="2" t="n">
-        <v>45244.09005195486</v>
+        <v>45244.09128347319</v>
       </c>
       <c r="G1322" t="inlineStr">
         <is>
@@ -33496,22 +33496,22 @@
     </row>
     <row r="1323">
       <c r="A1323" t="n">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B1323" t="n">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="C1323" t="n">
         <v>124</v>
       </c>
       <c r="D1323" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1323" t="n">
-        <v>20.890063</v>
+        <v>13.984872</v>
       </c>
       <c r="F1323" s="2" t="n">
-        <v>45244.09128347319</v>
+        <v>45244.09268533569</v>
       </c>
       <c r="G1323" t="inlineStr">
         <is>
@@ -33521,22 +33521,22 @@
     </row>
     <row r="1324">
       <c r="A1324" t="n">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B1324" t="n">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="C1324" t="n">
         <v>124</v>
       </c>
       <c r="D1324" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1324" t="n">
-        <v>13.984872</v>
+        <v>12.087255</v>
       </c>
       <c r="F1324" s="2" t="n">
-        <v>45244.09268533569</v>
+        <v>45244.09401840507</v>
       </c>
       <c r="G1324" t="inlineStr">
         <is>
@@ -33546,22 +33546,22 @@
     </row>
     <row r="1325">
       <c r="A1325" t="n">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B1325" t="n">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="C1325" t="n">
         <v>124</v>
       </c>
       <c r="D1325" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1325" t="n">
-        <v>12.087255</v>
+        <v>12.284084</v>
       </c>
       <c r="F1325" s="2" t="n">
-        <v>45244.09401840507</v>
+        <v>45244.09517104598</v>
       </c>
       <c r="G1325" t="inlineStr">
         <is>
@@ -33571,22 +33571,22 @@
     </row>
     <row r="1326">
       <c r="A1326" t="n">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="B1326" t="n">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="C1326" t="n">
         <v>124</v>
       </c>
       <c r="D1326" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1326" t="n">
-        <v>12.284084</v>
+        <v>11.383772</v>
       </c>
       <c r="F1326" s="2" t="n">
-        <v>45244.09517104598</v>
+        <v>45244.09668108557</v>
       </c>
       <c r="G1326" t="inlineStr">
         <is>
@@ -33596,22 +33596,22 @@
     </row>
     <row r="1327">
       <c r="A1327" t="n">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B1327" t="n">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="C1327" t="n">
         <v>124</v>
       </c>
       <c r="D1327" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1327" t="n">
-        <v>11.383772</v>
+        <v>20.758597</v>
       </c>
       <c r="F1327" s="2" t="n">
-        <v>45244.09668108557</v>
+        <v>45244.09749799991</v>
       </c>
       <c r="G1327" t="inlineStr">
         <is>
@@ -33621,22 +33621,22 @@
     </row>
     <row r="1328">
       <c r="A1328" t="n">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B1328" t="n">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="C1328" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D1328" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E1328" t="n">
-        <v>20.758597</v>
+        <v>10.194183</v>
       </c>
       <c r="F1328" s="2" t="n">
-        <v>45244.09749799991</v>
+        <v>45244.10803359854</v>
       </c>
       <c r="G1328" t="inlineStr">
         <is>
@@ -33646,22 +33646,22 @@
     </row>
     <row r="1329">
       <c r="A1329" t="n">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B1329" t="n">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="C1329" t="n">
         <v>125</v>
       </c>
       <c r="D1329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1329" t="n">
-        <v>10.194183</v>
+        <v>17.838361</v>
       </c>
       <c r="F1329" s="2" t="n">
-        <v>45244.10803359854</v>
+        <v>45244.10897118716</v>
       </c>
       <c r="G1329" t="inlineStr">
         <is>
@@ -33671,22 +33671,22 @@
     </row>
     <row r="1330">
       <c r="A1330" t="n">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B1330" t="n">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="C1330" t="n">
         <v>125</v>
       </c>
       <c r="D1330" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E1330" t="n">
-        <v>17.838361</v>
+        <v>10.783763</v>
       </c>
       <c r="F1330" s="2" t="n">
-        <v>45244.10897118716</v>
+        <v>45244.10984039338</v>
       </c>
       <c r="G1330" t="inlineStr">
         <is>
@@ -33696,22 +33696,22 @@
     </row>
     <row r="1331">
       <c r="A1331" t="n">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B1331" t="n">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="C1331" t="n">
         <v>125</v>
       </c>
       <c r="D1331" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1331" t="n">
-        <v>10.783763</v>
+        <v>11.406246</v>
       </c>
       <c r="F1331" s="2" t="n">
-        <v>45244.10984039338</v>
+        <v>45244.11040424248</v>
       </c>
       <c r="G1331" t="inlineStr">
         <is>
@@ -33721,22 +33721,22 @@
     </row>
     <row r="1332">
       <c r="A1332" t="n">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B1332" t="n">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="C1332" t="n">
         <v>125</v>
       </c>
       <c r="D1332" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1332" t="n">
-        <v>11.406246</v>
+        <v>10.306136</v>
       </c>
       <c r="F1332" s="2" t="n">
-        <v>45244.11040424248</v>
+        <v>45244.11138171552</v>
       </c>
       <c r="G1332" t="inlineStr">
         <is>
@@ -33746,22 +33746,22 @@
     </row>
     <row r="1333">
       <c r="A1333" t="n">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B1333" t="n">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="C1333" t="n">
         <v>125</v>
       </c>
       <c r="D1333" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1333" t="n">
-        <v>10.306136</v>
+        <v>18.699508</v>
       </c>
       <c r="F1333" s="2" t="n">
-        <v>45244.11138171552</v>
+        <v>45244.11225244397</v>
       </c>
       <c r="G1333" t="inlineStr">
         <is>
@@ -33771,22 +33771,22 @@
     </row>
     <row r="1334">
       <c r="A1334" t="n">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="B1334" t="n">
-        <v>2228</v>
+        <v>2233</v>
       </c>
       <c r="C1334" t="n">
         <v>125</v>
       </c>
       <c r="D1334" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E1334" t="n">
-        <v>18.699508</v>
+        <v>10.852321</v>
       </c>
       <c r="F1334" s="2" t="n">
-        <v>45244.11225244397</v>
+        <v>45244.11533537413</v>
       </c>
       <c r="G1334" t="inlineStr">
         <is>
@@ -33796,22 +33796,22 @@
     </row>
     <row r="1335">
       <c r="A1335" t="n">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B1335" t="n">
-        <v>2233</v>
+        <v>2235</v>
       </c>
       <c r="C1335" t="n">
         <v>125</v>
       </c>
       <c r="D1335" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1335" t="n">
-        <v>10.852321</v>
+        <v>10.813985</v>
       </c>
       <c r="F1335" s="2" t="n">
-        <v>45244.11533537413</v>
+        <v>45244.11701828358</v>
       </c>
       <c r="G1335" t="inlineStr">
         <is>
@@ -33821,22 +33821,22 @@
     </row>
     <row r="1336">
       <c r="A1336" t="n">
-        <v>1277</v>
+        <v>1287</v>
       </c>
       <c r="B1336" t="n">
-        <v>2235</v>
+        <v>2250</v>
       </c>
       <c r="C1336" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D1336" t="n">
         <v>14</v>
       </c>
       <c r="E1336" t="n">
-        <v>10.813985</v>
+        <v>11.728947</v>
       </c>
       <c r="F1336" s="2" t="n">
-        <v>45244.11701828358</v>
+        <v>45244.18623833552</v>
       </c>
       <c r="G1336" t="inlineStr">
         <is>
@@ -33846,22 +33846,22 @@
     </row>
     <row r="1337">
       <c r="A1337" t="n">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B1337" t="n">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="C1337" t="n">
         <v>126</v>
       </c>
       <c r="D1337" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1337" t="n">
-        <v>11.728947</v>
+        <v>10.374225</v>
       </c>
       <c r="F1337" s="2" t="n">
-        <v>45244.18623833552</v>
+        <v>45244.18796107803</v>
       </c>
       <c r="G1337" t="inlineStr">
         <is>
@@ -33871,22 +33871,22 @@
     </row>
     <row r="1338">
       <c r="A1338" t="n">
-        <v>1288</v>
+        <v>1304</v>
       </c>
       <c r="B1338" t="n">
-        <v>2252</v>
+        <v>2277</v>
       </c>
       <c r="C1338" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D1338" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E1338" t="n">
-        <v>10.374225</v>
+        <v>12.800254</v>
       </c>
       <c r="F1338" s="2" t="n">
-        <v>45244.18796107803</v>
+        <v>45244.23069364302</v>
       </c>
       <c r="G1338" t="inlineStr">
         <is>
@@ -33896,22 +33896,22 @@
     </row>
     <row r="1339">
       <c r="A1339" t="n">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B1339" t="n">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="C1339" t="n">
         <v>128</v>
       </c>
       <c r="D1339" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E1339" t="n">
-        <v>12.800254</v>
+        <v>19.894508</v>
       </c>
       <c r="F1339" s="2" t="n">
-        <v>45244.23069364302</v>
+        <v>45244.23341618539</v>
       </c>
       <c r="G1339" t="inlineStr">
         <is>
@@ -33921,22 +33921,22 @@
     </row>
     <row r="1340">
       <c r="A1340" t="n">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B1340" t="n">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="C1340" t="n">
         <v>128</v>
       </c>
       <c r="D1340" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1340" t="n">
-        <v>19.894508</v>
+        <v>13.273407</v>
       </c>
       <c r="F1340" s="2" t="n">
-        <v>45244.23341618539</v>
+        <v>45244.23443926325</v>
       </c>
       <c r="G1340" t="inlineStr">
         <is>
@@ -33946,22 +33946,22 @@
     </row>
     <row r="1341">
       <c r="A1341" t="n">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="B1341" t="n">
-        <v>2282</v>
+        <v>2290</v>
       </c>
       <c r="C1341" t="n">
         <v>128</v>
       </c>
       <c r="D1341" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E1341" t="n">
-        <v>13.273407</v>
+        <v>12.37771</v>
       </c>
       <c r="F1341" s="2" t="n">
-        <v>45244.23443926325</v>
+        <v>45244.24092515715</v>
       </c>
       <c r="G1341" t="inlineStr">
         <is>
@@ -33971,22 +33971,22 @@
     </row>
     <row r="1342">
       <c r="A1342" t="n">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B1342" t="n">
-        <v>2290</v>
+        <v>2292</v>
       </c>
       <c r="C1342" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D1342" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E1342" t="n">
-        <v>12.37771</v>
+        <v>10.886564</v>
       </c>
       <c r="F1342" s="2" t="n">
-        <v>45244.24092515715</v>
+        <v>45244.28454289032</v>
       </c>
       <c r="G1342" t="inlineStr">
         <is>
@@ -33996,22 +33996,22 @@
     </row>
     <row r="1343">
       <c r="A1343" t="n">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B1343" t="n">
-        <v>2292</v>
+        <v>2295</v>
       </c>
       <c r="C1343" t="n">
         <v>129</v>
       </c>
       <c r="D1343" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E1343" t="n">
-        <v>10.886564</v>
+        <v>17.215321</v>
       </c>
       <c r="F1343" s="2" t="n">
-        <v>45244.28454289032</v>
+        <v>45244.28698802536</v>
       </c>
       <c r="G1343" t="inlineStr">
         <is>
@@ -34021,22 +34021,22 @@
     </row>
     <row r="1344">
       <c r="A1344" t="n">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="B1344" t="n">
-        <v>2295</v>
+        <v>2298</v>
       </c>
       <c r="C1344" t="n">
         <v>129</v>
       </c>
       <c r="D1344" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1344" t="n">
-        <v>17.215321</v>
+        <v>14.740052</v>
       </c>
       <c r="F1344" s="2" t="n">
-        <v>45244.28698802536</v>
+        <v>45244.28970697992</v>
       </c>
       <c r="G1344" t="inlineStr">
         <is>
@@ -34046,22 +34046,22 @@
     </row>
     <row r="1345">
       <c r="A1345" t="n">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B1345" t="n">
-        <v>2298</v>
+        <v>2300</v>
       </c>
       <c r="C1345" t="n">
         <v>129</v>
       </c>
       <c r="D1345" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1345" t="n">
-        <v>14.740052</v>
+        <v>13.770057</v>
       </c>
       <c r="F1345" s="2" t="n">
-        <v>45244.28970697992</v>
+        <v>45244.29110425364</v>
       </c>
       <c r="G1345" t="inlineStr">
         <is>
@@ -34071,22 +34071,22 @@
     </row>
     <row r="1346">
       <c r="A1346" t="n">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B1346" t="n">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="C1346" t="n">
         <v>129</v>
       </c>
       <c r="D1346" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1346" t="n">
-        <v>13.770057</v>
+        <v>21.818587</v>
       </c>
       <c r="F1346" s="2" t="n">
-        <v>45244.29110425364</v>
+        <v>45244.29216084067</v>
       </c>
       <c r="G1346" t="inlineStr">
         <is>
@@ -34096,22 +34096,22 @@
     </row>
     <row r="1347">
       <c r="A1347" t="n">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B1347" t="n">
-        <v>2301</v>
+        <v>2303</v>
       </c>
       <c r="C1347" t="n">
         <v>129</v>
       </c>
       <c r="D1347" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1347" t="n">
-        <v>21.818587</v>
+        <v>13.166181</v>
       </c>
       <c r="F1347" s="2" t="n">
-        <v>45244.29216084067</v>
+        <v>45244.29344209887</v>
       </c>
       <c r="G1347" t="inlineStr">
         <is>
@@ -34121,22 +34121,22 @@
     </row>
     <row r="1348">
       <c r="A1348" t="n">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B1348" t="n">
-        <v>2303</v>
+        <v>2305</v>
       </c>
       <c r="C1348" t="n">
         <v>129</v>
       </c>
       <c r="D1348" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1348" t="n">
-        <v>13.166181</v>
+        <v>13.423876</v>
       </c>
       <c r="F1348" s="2" t="n">
-        <v>45244.29344209887</v>
+        <v>45244.29510147886</v>
       </c>
       <c r="G1348" t="inlineStr">
         <is>
@@ -34146,22 +34146,22 @@
     </row>
     <row r="1349">
       <c r="A1349" t="n">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B1349" t="n">
-        <v>2305</v>
+        <v>2307</v>
       </c>
       <c r="C1349" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D1349" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E1349" t="n">
-        <v>13.423876</v>
+        <v>11.845546</v>
       </c>
       <c r="F1349" s="2" t="n">
-        <v>45244.29510147886</v>
+        <v>45244.31195151938</v>
       </c>
       <c r="G1349" t="inlineStr">
         <is>
@@ -34171,22 +34171,22 @@
     </row>
     <row r="1350">
       <c r="A1350" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B1350" t="n">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="C1350" t="n">
         <v>130</v>
       </c>
       <c r="D1350" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1350" t="n">
-        <v>11.845546</v>
+        <v>11.37701</v>
       </c>
       <c r="F1350" s="2" t="n">
-        <v>45244.31195151938</v>
+        <v>45244.31276604225</v>
       </c>
       <c r="G1350" t="inlineStr">
         <is>
@@ -34196,22 +34196,22 @@
     </row>
     <row r="1351">
       <c r="A1351" t="n">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B1351" t="n">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="C1351" t="n">
         <v>130</v>
       </c>
       <c r="D1351" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1351" t="n">
-        <v>11.37701</v>
+        <v>12.062459</v>
       </c>
       <c r="F1351" s="2" t="n">
-        <v>45244.31276604225</v>
+        <v>45244.31349896399</v>
       </c>
       <c r="G1351" t="inlineStr">
         <is>
@@ -34221,22 +34221,22 @@
     </row>
     <row r="1352">
       <c r="A1352" t="n">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B1352" t="n">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C1352" t="n">
         <v>130</v>
       </c>
       <c r="D1352" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1352" t="n">
-        <v>12.062459</v>
+        <v>13.158561</v>
       </c>
       <c r="F1352" s="2" t="n">
-        <v>45244.31349896399</v>
+        <v>45244.31407134126</v>
       </c>
       <c r="G1352" t="inlineStr">
         <is>
@@ -34246,22 +34246,22 @@
     </row>
     <row r="1353">
       <c r="A1353" t="n">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B1353" t="n">
-        <v>2310</v>
+        <v>2313</v>
       </c>
       <c r="C1353" t="n">
         <v>130</v>
       </c>
       <c r="D1353" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1353" t="n">
-        <v>13.158561</v>
+        <v>14.98579</v>
       </c>
       <c r="F1353" s="2" t="n">
-        <v>45244.31407134126</v>
+        <v>45244.31639694019</v>
       </c>
       <c r="G1353" t="inlineStr">
         <is>
@@ -34271,22 +34271,22 @@
     </row>
     <row r="1354">
       <c r="A1354" t="n">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="B1354" t="n">
-        <v>2313</v>
+        <v>2319</v>
       </c>
       <c r="C1354" t="n">
         <v>130</v>
       </c>
       <c r="D1354" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E1354" t="n">
-        <v>14.98579</v>
+        <v>16.341578</v>
       </c>
       <c r="F1354" s="2" t="n">
-        <v>45244.31639694019</v>
+        <v>45244.32250588341</v>
       </c>
       <c r="G1354" t="inlineStr">
         <is>
@@ -34296,22 +34296,22 @@
     </row>
     <row r="1355">
       <c r="A1355" t="n">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B1355" t="n">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="C1355" t="n">
         <v>130</v>
       </c>
       <c r="D1355" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1355" t="n">
-        <v>16.341578</v>
+        <v>13.065833</v>
       </c>
       <c r="F1355" s="2" t="n">
-        <v>45244.32250588341</v>
+        <v>45244.32379501537</v>
       </c>
       <c r="G1355" t="inlineStr">
         <is>
@@ -34321,22 +34321,22 @@
     </row>
     <row r="1356">
       <c r="A1356" t="n">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="B1356" t="n">
-        <v>2320</v>
+        <v>2325</v>
       </c>
       <c r="C1356" t="n">
         <v>130</v>
       </c>
       <c r="D1356" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E1356" t="n">
-        <v>13.065833</v>
+        <v>14.567211</v>
       </c>
       <c r="F1356" s="2" t="n">
-        <v>45244.32379501537</v>
+        <v>45244.32830957702</v>
       </c>
       <c r="G1356" t="inlineStr">
         <is>
@@ -34346,22 +34346,22 @@
     </row>
     <row r="1357">
       <c r="A1357" t="n">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="B1357" t="n">
-        <v>2325</v>
+        <v>2328</v>
       </c>
       <c r="C1357" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D1357" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E1357" t="n">
-        <v>14.567211</v>
+        <v>10.22613</v>
       </c>
       <c r="F1357" s="2" t="n">
-        <v>45244.32830957702</v>
+        <v>45244.33734981716</v>
       </c>
       <c r="G1357" t="inlineStr">
         <is>
@@ -34371,22 +34371,22 @@
     </row>
     <row r="1358">
       <c r="A1358" t="n">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B1358" t="n">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="C1358" t="n">
         <v>131</v>
       </c>
       <c r="D1358" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1358" t="n">
-        <v>10.22613</v>
+        <v>19.656897</v>
       </c>
       <c r="F1358" s="2" t="n">
-        <v>45244.33734981716</v>
+        <v>45244.33824705613</v>
       </c>
       <c r="G1358" t="inlineStr">
         <is>
@@ -34396,22 +34396,22 @@
     </row>
     <row r="1359">
       <c r="A1359" t="n">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="B1359" t="n">
-        <v>2329</v>
+        <v>2333</v>
       </c>
       <c r="C1359" t="n">
         <v>131</v>
       </c>
       <c r="D1359" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1359" t="n">
-        <v>19.656897</v>
+        <v>23.919673</v>
       </c>
       <c r="F1359" s="2" t="n">
-        <v>45244.33824705613</v>
+        <v>45244.34088121488</v>
       </c>
       <c r="G1359" t="inlineStr">
         <is>
@@ -34421,22 +34421,22 @@
     </row>
     <row r="1360">
       <c r="A1360" t="n">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="B1360" t="n">
-        <v>2333</v>
+        <v>2335</v>
       </c>
       <c r="C1360" t="n">
         <v>131</v>
       </c>
       <c r="D1360" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1360" t="n">
-        <v>23.919673</v>
+        <v>14.096594</v>
       </c>
       <c r="F1360" s="2" t="n">
-        <v>45244.34088121488</v>
+        <v>45244.3418630423</v>
       </c>
       <c r="G1360" t="inlineStr">
         <is>
@@ -34446,22 +34446,22 @@
     </row>
     <row r="1361">
       <c r="A1361" t="n">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B1361" t="n">
-        <v>2335</v>
+        <v>2337</v>
       </c>
       <c r="C1361" t="n">
         <v>131</v>
       </c>
       <c r="D1361" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1361" t="n">
-        <v>14.096594</v>
+        <v>12.755136</v>
       </c>
       <c r="F1361" s="2" t="n">
-        <v>45244.3418630423</v>
+        <v>45244.34330984638</v>
       </c>
       <c r="G1361" t="inlineStr">
         <is>
@@ -34471,22 +34471,22 @@
     </row>
     <row r="1362">
       <c r="A1362" t="n">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B1362" t="n">
-        <v>2337</v>
+        <v>2339</v>
       </c>
       <c r="C1362" t="n">
         <v>131</v>
       </c>
       <c r="D1362" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1362" t="n">
-        <v>12.755136</v>
+        <v>11.926433</v>
       </c>
       <c r="F1362" s="2" t="n">
-        <v>45244.34330984638</v>
+        <v>45244.34465765557</v>
       </c>
       <c r="G1362" t="inlineStr">
         <is>
@@ -34496,22 +34496,22 @@
     </row>
     <row r="1363">
       <c r="A1363" t="n">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B1363" t="n">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="C1363" t="n">
         <v>131</v>
       </c>
       <c r="D1363" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1363" t="n">
-        <v>11.926433</v>
+        <v>10.671486</v>
       </c>
       <c r="F1363" s="2" t="n">
-        <v>45244.34465765557</v>
+        <v>45244.34542594876</v>
       </c>
       <c r="G1363" t="inlineStr">
         <is>
@@ -34521,22 +34521,22 @@
     </row>
     <row r="1364">
       <c r="A1364" t="n">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B1364" t="n">
-        <v>2340</v>
+        <v>2342</v>
       </c>
       <c r="C1364" t="n">
         <v>131</v>
       </c>
       <c r="D1364" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1364" t="n">
-        <v>10.671486</v>
+        <v>11.319923</v>
       </c>
       <c r="F1364" s="2" t="n">
-        <v>45244.34542594876</v>
+        <v>45244.34702929483</v>
       </c>
       <c r="G1364" t="inlineStr">
         <is>
@@ -34546,22 +34546,22 @@
     </row>
     <row r="1365">
       <c r="A1365" t="n">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="B1365" t="n">
-        <v>2342</v>
+        <v>2347</v>
       </c>
       <c r="C1365" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D1365" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E1365" t="n">
-        <v>11.319923</v>
+        <v>12.079016</v>
       </c>
       <c r="F1365" s="2" t="n">
-        <v>45244.34702929483</v>
+        <v>45244.36721665888</v>
       </c>
       <c r="G1365" t="inlineStr">
         <is>
@@ -34571,22 +34571,22 @@
     </row>
     <row r="1366">
       <c r="A1366" t="n">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B1366" t="n">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="C1366" t="n">
         <v>132</v>
       </c>
       <c r="D1366" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1366" t="n">
-        <v>12.079016</v>
+        <v>11.856954</v>
       </c>
       <c r="F1366" s="2" t="n">
-        <v>45244.36721665888</v>
+        <v>45244.36918178697</v>
       </c>
       <c r="G1366" t="inlineStr">
         <is>
@@ -34596,22 +34596,22 @@
     </row>
     <row r="1367">
       <c r="A1367" t="n">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B1367" t="n">
-        <v>2349</v>
+        <v>2352</v>
       </c>
       <c r="C1367" t="n">
         <v>132</v>
       </c>
       <c r="D1367" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E1367" t="n">
-        <v>11.856954</v>
+        <v>15.108744</v>
       </c>
       <c r="F1367" s="2" t="n">
-        <v>45244.36918178697</v>
+        <v>45244.37167819445</v>
       </c>
       <c r="G1367" t="inlineStr">
         <is>
@@ -34621,22 +34621,22 @@
     </row>
     <row r="1368">
       <c r="A1368" t="n">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B1368" t="n">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="C1368" t="n">
         <v>132</v>
       </c>
       <c r="D1368" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1368" t="n">
-        <v>15.108744</v>
+        <v>9.697596000000001</v>
       </c>
       <c r="F1368" s="2" t="n">
-        <v>45244.37167819445</v>
+        <v>45244.3732363606</v>
       </c>
       <c r="G1368" t="inlineStr">
         <is>
@@ -34646,22 +34646,22 @@
     </row>
     <row r="1369">
       <c r="A1369" t="n">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B1369" t="n">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="C1369" t="n">
         <v>132</v>
       </c>
       <c r="D1369" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1369" t="n">
-        <v>9.697596000000001</v>
+        <v>23.047951</v>
       </c>
       <c r="F1369" s="2" t="n">
-        <v>45244.3732363606</v>
+        <v>45244.37403904014</v>
       </c>
       <c r="G1369" t="inlineStr">
         <is>
@@ -34671,22 +34671,22 @@
     </row>
     <row r="1370">
       <c r="A1370" t="n">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B1370" t="n">
-        <v>2355</v>
+        <v>2360</v>
       </c>
       <c r="C1370" t="n">
         <v>132</v>
       </c>
       <c r="D1370" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E1370" t="n">
-        <v>23.047951</v>
+        <v>11.759413</v>
       </c>
       <c r="F1370" s="2" t="n">
-        <v>45244.37403904014</v>
+        <v>45244.37810986231</v>
       </c>
       <c r="G1370" t="inlineStr">
         <is>
@@ -34696,22 +34696,22 @@
     </row>
     <row r="1371">
       <c r="A1371" t="n">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="B1371" t="n">
-        <v>2360</v>
+        <v>2363</v>
       </c>
       <c r="C1371" t="n">
         <v>132</v>
       </c>
       <c r="D1371" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E1371" t="n">
-        <v>11.759413</v>
+        <v>12.389119</v>
       </c>
       <c r="F1371" s="2" t="n">
-        <v>45244.37810986231</v>
+        <v>45244.38090437042</v>
       </c>
       <c r="G1371" t="inlineStr">
         <is>
@@ -34721,22 +34721,22 @@
     </row>
     <row r="1372">
       <c r="A1372" t="n">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B1372" t="n">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="C1372" t="n">
         <v>132</v>
       </c>
       <c r="D1372" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1372" t="n">
-        <v>12.389119</v>
+        <v>29.077672</v>
       </c>
       <c r="F1372" s="2" t="n">
-        <v>45244.38090437042</v>
+        <v>45244.38199208419</v>
       </c>
       <c r="G1372" t="inlineStr">
         <is>
@@ -34746,22 +34746,22 @@
     </row>
     <row r="1373">
       <c r="A1373" t="n">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B1373" t="n">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="C1373" t="n">
         <v>132</v>
       </c>
       <c r="D1373" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1373" t="n">
-        <v>29.077672</v>
+        <v>11.314755</v>
       </c>
       <c r="F1373" s="2" t="n">
-        <v>45244.38199208419</v>
+        <v>45244.38250290988</v>
       </c>
       <c r="G1373" t="inlineStr">
         <is>
@@ -34771,22 +34771,22 @@
     </row>
     <row r="1374">
       <c r="A1374" t="n">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="B1374" t="n">
-        <v>2365</v>
+        <v>2368</v>
       </c>
       <c r="C1374" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D1374" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E1374" t="n">
-        <v>11.314755</v>
+        <v>12.851141</v>
       </c>
       <c r="F1374" s="2" t="n">
-        <v>45244.38250290988</v>
+        <v>45244.39278950416</v>
       </c>
       <c r="G1374" t="inlineStr">
         <is>
@@ -34796,22 +34796,22 @@
     </row>
     <row r="1375">
       <c r="A1375" t="n">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B1375" t="n">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="C1375" t="n">
         <v>133</v>
       </c>
       <c r="D1375" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1375" t="n">
-        <v>12.851141</v>
+        <v>24.587477</v>
       </c>
       <c r="F1375" s="2" t="n">
-        <v>45244.39278950416</v>
+        <v>45244.39399860608</v>
       </c>
       <c r="G1375" t="inlineStr">
         <is>
@@ -34821,22 +34821,22 @@
     </row>
     <row r="1376">
       <c r="A1376" t="n">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B1376" t="n">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="C1376" t="n">
         <v>133</v>
       </c>
       <c r="D1376" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1376" t="n">
-        <v>24.587477</v>
+        <v>13.349715</v>
       </c>
       <c r="F1376" s="2" t="n">
-        <v>45244.39399860608</v>
+        <v>45244.39448810899</v>
       </c>
       <c r="G1376" t="inlineStr">
         <is>
@@ -34846,22 +34846,22 @@
     </row>
     <row r="1377">
       <c r="A1377" t="n">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B1377" t="n">
-        <v>2370</v>
+        <v>2372</v>
       </c>
       <c r="C1377" t="n">
         <v>133</v>
       </c>
       <c r="D1377" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1377" t="n">
-        <v>13.349715</v>
+        <v>26.603149</v>
       </c>
       <c r="F1377" s="2" t="n">
-        <v>45244.39448810899</v>
+        <v>45244.3962457919</v>
       </c>
       <c r="G1377" t="inlineStr">
         <is>
@@ -34871,22 +34871,22 @@
     </row>
     <row r="1378">
       <c r="A1378" t="n">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="B1378" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="C1378" t="n">
         <v>133</v>
       </c>
       <c r="D1378" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1378" t="n">
-        <v>26.603149</v>
+        <v>13.504976</v>
       </c>
       <c r="F1378" s="2" t="n">
-        <v>45244.3962457919</v>
+        <v>45244.39843028992</v>
       </c>
       <c r="G1378" t="inlineStr">
         <is>
@@ -34896,22 +34896,22 @@
     </row>
     <row r="1379">
       <c r="A1379" t="n">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B1379" t="n">
-        <v>2375</v>
+        <v>2378</v>
       </c>
       <c r="C1379" t="n">
         <v>133</v>
       </c>
       <c r="D1379" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E1379" t="n">
-        <v>13.504976</v>
+        <v>27.34211</v>
       </c>
       <c r="F1379" s="2" t="n">
-        <v>45244.39843028992</v>
+        <v>45244.40099620744</v>
       </c>
       <c r="G1379" t="inlineStr">
         <is>
@@ -34921,22 +34921,22 @@
     </row>
     <row r="1380">
       <c r="A1380" t="n">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B1380" t="n">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="C1380" t="n">
         <v>133</v>
       </c>
       <c r="D1380" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1380" t="n">
-        <v>27.34211</v>
+        <v>11.801562</v>
       </c>
       <c r="F1380" s="2" t="n">
-        <v>45244.40099620744</v>
+        <v>45244.40149917898</v>
       </c>
       <c r="G1380" t="inlineStr">
         <is>
@@ -34946,22 +34946,22 @@
     </row>
     <row r="1381">
       <c r="A1381" t="n">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B1381" t="n">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="C1381" t="n">
         <v>133</v>
       </c>
       <c r="D1381" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1381" t="n">
-        <v>11.801562</v>
+        <v>12.795958</v>
       </c>
       <c r="F1381" s="2" t="n">
-        <v>45244.40149917898</v>
+        <v>45244.40242864312</v>
       </c>
       <c r="G1381" t="inlineStr">
         <is>
@@ -34971,22 +34971,22 @@
     </row>
     <row r="1382">
       <c r="A1382" t="n">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B1382" t="n">
-        <v>2380</v>
+        <v>2382</v>
       </c>
       <c r="C1382" t="n">
         <v>133</v>
       </c>
       <c r="D1382" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1382" t="n">
-        <v>12.795958</v>
+        <v>12.349767</v>
       </c>
       <c r="F1382" s="2" t="n">
-        <v>45244.40242864312</v>
+        <v>45244.4040626007</v>
       </c>
       <c r="G1382" t="inlineStr">
         <is>
@@ -34996,22 +34996,22 @@
     </row>
     <row r="1383">
       <c r="A1383" t="n">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B1383" t="n">
-        <v>2382</v>
+        <v>2385</v>
       </c>
       <c r="C1383" t="n">
         <v>133</v>
       </c>
       <c r="D1383" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1383" t="n">
-        <v>12.349767</v>
+        <v>12.663664</v>
       </c>
       <c r="F1383" s="2" t="n">
-        <v>45244.4040626007</v>
+        <v>45244.40638197499</v>
       </c>
       <c r="G1383" t="inlineStr">
         <is>
@@ -35021,22 +35021,22 @@
     </row>
     <row r="1384">
       <c r="A1384" t="n">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="B1384" t="n">
-        <v>2385</v>
+        <v>2388</v>
       </c>
       <c r="C1384" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D1384" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E1384" t="n">
-        <v>12.663664</v>
+        <v>16.617143</v>
       </c>
       <c r="F1384" s="2" t="n">
-        <v>45244.40638197499</v>
+        <v>45244.43720690598</v>
       </c>
       <c r="G1384" t="inlineStr">
         <is>
@@ -35046,22 +35046,22 @@
     </row>
     <row r="1385">
       <c r="A1385" t="n">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B1385" t="n">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="C1385" t="n">
         <v>134</v>
       </c>
       <c r="D1385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1385" t="n">
-        <v>16.617143</v>
+        <v>11.92089</v>
       </c>
       <c r="F1385" s="2" t="n">
-        <v>45244.43720690598</v>
+        <v>45244.43765318159</v>
       </c>
       <c r="G1385" t="inlineStr">
         <is>
@@ -35071,22 +35071,22 @@
     </row>
     <row r="1386">
       <c r="A1386" t="n">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B1386" t="n">
-        <v>2389</v>
+        <v>2390</v>
       </c>
       <c r="C1386" t="n">
         <v>134</v>
       </c>
       <c r="D1386" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1386" t="n">
-        <v>11.92089</v>
+        <v>14.952992</v>
       </c>
       <c r="F1386" s="2" t="n">
-        <v>45244.43765318159</v>
+        <v>45244.4386572658</v>
       </c>
       <c r="G1386" t="inlineStr">
         <is>
@@ -35096,22 +35096,22 @@
     </row>
     <row r="1387">
       <c r="A1387" t="n">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B1387" t="n">
-        <v>2390</v>
+        <v>2392</v>
       </c>
       <c r="C1387" t="n">
         <v>134</v>
       </c>
       <c r="D1387" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1387" t="n">
-        <v>14.952992</v>
+        <v>12.75887</v>
       </c>
       <c r="F1387" s="2" t="n">
-        <v>45244.4386572658</v>
+        <v>45244.43972148556</v>
       </c>
       <c r="G1387" t="inlineStr">
         <is>
@@ -35121,22 +35121,22 @@
     </row>
     <row r="1388">
       <c r="A1388" t="n">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="B1388" t="n">
-        <v>2392</v>
+        <v>2395</v>
       </c>
       <c r="C1388" t="n">
         <v>134</v>
       </c>
       <c r="D1388" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1388" t="n">
-        <v>12.75887</v>
+        <v>12.749963</v>
       </c>
       <c r="F1388" s="2" t="n">
-        <v>45244.43972148556</v>
+        <v>45244.44210686875</v>
       </c>
       <c r="G1388" t="inlineStr">
         <is>
@@ -35146,22 +35146,22 @@
     </row>
     <row r="1389">
       <c r="A1389" t="n">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B1389" t="n">
-        <v>2395</v>
+        <v>2397</v>
       </c>
       <c r="C1389" t="n">
         <v>134</v>
       </c>
       <c r="D1389" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1389" t="n">
-        <v>12.749963</v>
+        <v>12.571585</v>
       </c>
       <c r="F1389" s="2" t="n">
-        <v>45244.44210686875</v>
+        <v>45244.44405934111</v>
       </c>
       <c r="G1389" t="inlineStr">
         <is>
@@ -35171,22 +35171,22 @@
     </row>
     <row r="1390">
       <c r="A1390" t="n">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="B1390" t="n">
-        <v>2397</v>
+        <v>2402</v>
       </c>
       <c r="C1390" t="n">
         <v>134</v>
       </c>
       <c r="D1390" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E1390" t="n">
-        <v>12.571585</v>
+        <v>12.249836</v>
       </c>
       <c r="F1390" s="2" t="n">
-        <v>45244.44405934111</v>
+        <v>45244.44790590276</v>
       </c>
       <c r="G1390" t="inlineStr">
         <is>
@@ -35196,22 +35196,22 @@
     </row>
     <row r="1391">
       <c r="A1391" t="n">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B1391" t="n">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="C1391" t="n">
         <v>134</v>
       </c>
       <c r="D1391" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1391" t="n">
-        <v>12.249836</v>
+        <v>12.661132</v>
       </c>
       <c r="F1391" s="2" t="n">
-        <v>45244.44790590276</v>
+        <v>45244.44871643459</v>
       </c>
       <c r="G1391" t="inlineStr">
         <is>
@@ -35221,22 +35221,22 @@
     </row>
     <row r="1392">
       <c r="A1392" t="n">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B1392" t="n">
-        <v>2403</v>
+        <v>2405</v>
       </c>
       <c r="C1392" t="n">
         <v>134</v>
       </c>
       <c r="D1392" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1392" t="n">
-        <v>12.661132</v>
+        <v>12.4873</v>
       </c>
       <c r="F1392" s="2" t="n">
-        <v>45244.44871643459</v>
+        <v>45244.4507016041</v>
       </c>
       <c r="G1392" t="inlineStr">
         <is>
@@ -35246,22 +35246,22 @@
     </row>
     <row r="1393">
       <c r="A1393" t="n">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B1393" t="n">
-        <v>2405</v>
+        <v>2407</v>
       </c>
       <c r="C1393" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D1393" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E1393" t="n">
-        <v>12.4873</v>
+        <v>11.919058</v>
       </c>
       <c r="F1393" s="2" t="n">
-        <v>45244.4507016041</v>
+        <v>45244.46372957574</v>
       </c>
       <c r="G1393" t="inlineStr">
         <is>
@@ -35271,22 +35271,22 @@
     </row>
     <row r="1394">
       <c r="A1394" t="n">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B1394" t="n">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="C1394" t="n">
         <v>135</v>
       </c>
       <c r="D1394" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1394" t="n">
-        <v>11.919058</v>
+        <v>12.365142</v>
       </c>
       <c r="F1394" s="2" t="n">
-        <v>45244.46372957574</v>
+        <v>45244.46458035724</v>
       </c>
       <c r="G1394" t="inlineStr">
         <is>
@@ -35296,22 +35296,22 @@
     </row>
     <row r="1395">
       <c r="A1395" t="n">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B1395" t="n">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="C1395" t="n">
         <v>135</v>
       </c>
       <c r="D1395" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1395" t="n">
-        <v>12.365142</v>
+        <v>10.621779</v>
       </c>
       <c r="F1395" s="2" t="n">
-        <v>45244.46458035724</v>
+        <v>45244.46505171331</v>
       </c>
       <c r="G1395" t="inlineStr">
         <is>
@@ -35321,22 +35321,22 @@
     </row>
     <row r="1396">
       <c r="A1396" t="n">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="B1396" t="n">
-        <v>2409</v>
+        <v>2413</v>
       </c>
       <c r="C1396" t="n">
         <v>135</v>
       </c>
       <c r="D1396" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1396" t="n">
-        <v>10.621779</v>
+        <v>27.650062</v>
       </c>
       <c r="F1396" s="2" t="n">
-        <v>45244.46505171331</v>
+        <v>45244.46830951058</v>
       </c>
       <c r="G1396" t="inlineStr">
         <is>
@@ -35346,22 +35346,22 @@
     </row>
     <row r="1397">
       <c r="A1397" t="n">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="B1397" t="n">
-        <v>2413</v>
+        <v>2414</v>
       </c>
       <c r="C1397" t="n">
         <v>135</v>
       </c>
       <c r="D1397" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1397" t="n">
-        <v>27.650062</v>
+        <v>11.981177</v>
       </c>
       <c r="F1397" s="2" t="n">
-        <v>45244.46830951058</v>
+        <v>45244.46878266177</v>
       </c>
       <c r="G1397" t="inlineStr">
         <is>
@@ -35371,22 +35371,22 @@
     </row>
     <row r="1398">
       <c r="A1398" t="n">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="B1398" t="n">
-        <v>2414</v>
+        <v>2417</v>
       </c>
       <c r="C1398" t="n">
         <v>135</v>
       </c>
       <c r="D1398" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E1398" t="n">
-        <v>11.981177</v>
+        <v>13.733957</v>
       </c>
       <c r="F1398" s="2" t="n">
-        <v>45244.46878266177</v>
+        <v>45244.47089361282</v>
       </c>
       <c r="G1398" t="inlineStr">
         <is>
@@ -35396,22 +35396,22 @@
     </row>
     <row r="1399">
       <c r="A1399" t="n">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="B1399" t="n">
-        <v>2417</v>
+        <v>2420</v>
       </c>
       <c r="C1399" t="n">
         <v>135</v>
       </c>
       <c r="D1399" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1399" t="n">
-        <v>13.733957</v>
+        <v>10.606179</v>
       </c>
       <c r="F1399" s="2" t="n">
-        <v>45244.47089361282</v>
+        <v>45244.47286509934</v>
       </c>
       <c r="G1399" t="inlineStr">
         <is>
@@ -35421,22 +35421,22 @@
     </row>
     <row r="1400">
       <c r="A1400" t="n">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B1400" t="n">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="C1400" t="n">
         <v>135</v>
       </c>
       <c r="D1400" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1400" t="n">
-        <v>10.606179</v>
+        <v>10.281935</v>
       </c>
       <c r="F1400" s="2" t="n">
-        <v>45244.47286509934</v>
+        <v>45244.47415124966</v>
       </c>
       <c r="G1400" t="inlineStr">
         <is>
@@ -35446,22 +35446,22 @@
     </row>
     <row r="1401">
       <c r="A1401" t="n">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="B1401" t="n">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="C1401" t="n">
         <v>135</v>
       </c>
       <c r="D1401" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1401" t="n">
-        <v>10.281935</v>
+        <v>10.49509</v>
       </c>
       <c r="F1401" s="2" t="n">
-        <v>45244.47415124966</v>
+        <v>45244.4747542703</v>
       </c>
       <c r="G1401" t="inlineStr">
         <is>
@@ -35471,22 +35471,22 @@
     </row>
     <row r="1402">
       <c r="A1402" t="n">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="B1402" t="n">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="C1402" t="n">
         <v>135</v>
       </c>
       <c r="D1402" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1402" t="n">
-        <v>10.49509</v>
+        <v>10.883242</v>
       </c>
       <c r="F1402" s="2" t="n">
-        <v>45244.4747542703</v>
+        <v>45244.47605821664</v>
       </c>
       <c r="G1402" t="inlineStr">
         <is>
@@ -35496,22 +35496,22 @@
     </row>
     <row r="1403">
       <c r="A1403" t="n">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="B1403" t="n">
-        <v>2425</v>
+        <v>2430</v>
       </c>
       <c r="C1403" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D1403" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E1403" t="n">
-        <v>10.883242</v>
+        <v>11.554522</v>
       </c>
       <c r="F1403" s="2" t="n">
-        <v>45244.47605821664</v>
+        <v>45244.48645104799</v>
       </c>
       <c r="G1403" t="inlineStr">
         <is>
@@ -35521,22 +35521,22 @@
     </row>
     <row r="1404">
       <c r="A1404" t="n">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B1404" t="n">
-        <v>2430</v>
+        <v>2433</v>
       </c>
       <c r="C1404" t="n">
         <v>136</v>
       </c>
       <c r="D1404" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1404" t="n">
-        <v>11.554522</v>
+        <v>12.79826</v>
       </c>
       <c r="F1404" s="2" t="n">
-        <v>45244.48645104799</v>
+        <v>45244.4886255196</v>
       </c>
       <c r="G1404" t="inlineStr">
         <is>
@@ -35546,22 +35546,22 @@
     </row>
     <row r="1405">
       <c r="A1405" t="n">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B1405" t="n">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="C1405" t="n">
         <v>136</v>
       </c>
       <c r="D1405" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1405" t="n">
-        <v>12.79826</v>
+        <v>18.921124</v>
       </c>
       <c r="F1405" s="2" t="n">
-        <v>45244.4886255196</v>
+        <v>45244.48960868598</v>
       </c>
       <c r="G1405" t="inlineStr">
         <is>
@@ -35571,22 +35571,22 @@
     </row>
     <row r="1406">
       <c r="A1406" t="n">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B1406" t="n">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="C1406" t="n">
         <v>136</v>
       </c>
       <c r="D1406" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1406" t="n">
-        <v>18.921124</v>
+        <v>11.293859</v>
       </c>
       <c r="F1406" s="2" t="n">
-        <v>45244.48960868598</v>
+        <v>45244.49016622595</v>
       </c>
       <c r="G1406" t="inlineStr">
         <is>
@@ -35596,22 +35596,22 @@
     </row>
     <row r="1407">
       <c r="A1407" t="n">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B1407" t="n">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="C1407" t="n">
         <v>136</v>
       </c>
       <c r="D1407" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1407" t="n">
-        <v>11.293859</v>
+        <v>11.82153</v>
       </c>
       <c r="F1407" s="2" t="n">
-        <v>45244.49016622595</v>
+        <v>45244.49175595852</v>
       </c>
       <c r="G1407" t="inlineStr">
         <is>
@@ -35621,22 +35621,22 @@
     </row>
     <row r="1408">
       <c r="A1408" t="n">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="B1408" t="n">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="C1408" t="n">
         <v>136</v>
       </c>
       <c r="D1408" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1408" t="n">
-        <v>11.82153</v>
+        <v>22.436185</v>
       </c>
       <c r="F1408" s="2" t="n">
-        <v>45244.49175595852</v>
+        <v>45244.49315069988</v>
       </c>
       <c r="G1408" t="inlineStr">
         <is>
@@ -35646,22 +35646,22 @@
     </row>
     <row r="1409">
       <c r="A1409" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B1409" t="n">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="C1409" t="n">
         <v>136</v>
       </c>
       <c r="D1409" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1409" t="n">
-        <v>22.436185</v>
+        <v>13.782659</v>
       </c>
       <c r="F1409" s="2" t="n">
-        <v>45244.49315069988</v>
+        <v>45244.49380777294</v>
       </c>
       <c r="G1409" t="inlineStr">
         <is>
@@ -35671,22 +35671,22 @@
     </row>
     <row r="1410">
       <c r="A1410" t="n">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B1410" t="n">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="C1410" t="n">
         <v>136</v>
       </c>
       <c r="D1410" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1410" t="n">
-        <v>13.782659</v>
+        <v>12.998137</v>
       </c>
       <c r="F1410" s="2" t="n">
-        <v>45244.49380777294</v>
+        <v>45244.49494823582</v>
       </c>
       <c r="G1410" t="inlineStr">
         <is>
@@ -35696,22 +35696,22 @@
     </row>
     <row r="1411">
       <c r="A1411" t="n">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="B1411" t="n">
-        <v>2440</v>
+        <v>2442</v>
       </c>
       <c r="C1411" t="n">
         <v>136</v>
       </c>
       <c r="D1411" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1411" t="n">
-        <v>12.998137</v>
+        <v>12.831376</v>
       </c>
       <c r="F1411" s="2" t="n">
-        <v>45244.49494823582</v>
+        <v>45244.49675169531</v>
       </c>
       <c r="G1411" t="inlineStr">
         <is>
@@ -35721,22 +35721,22 @@
     </row>
     <row r="1412">
       <c r="A1412" t="n">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B1412" t="n">
-        <v>2442</v>
+        <v>2445</v>
       </c>
       <c r="C1412" t="n">
         <v>136</v>
       </c>
       <c r="D1412" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1412" t="n">
-        <v>12.831376</v>
+        <v>12.206384</v>
       </c>
       <c r="F1412" s="2" t="n">
-        <v>45244.49675169531</v>
+        <v>45244.49961837163</v>
       </c>
       <c r="G1412" t="inlineStr">
         <is>
@@ -35746,22 +35746,22 @@
     </row>
     <row r="1413">
       <c r="A1413" t="n">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="B1413" t="n">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="C1413" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D1413" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E1413" t="n">
-        <v>12.206384</v>
+        <v>11.278881</v>
       </c>
       <c r="F1413" s="2" t="n">
-        <v>45244.49961837163</v>
+        <v>45244.509967356</v>
       </c>
       <c r="G1413" t="inlineStr">
         <is>
@@ -35771,22 +35771,22 @@
     </row>
     <row r="1414">
       <c r="A1414" t="n">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B1414" t="n">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="C1414" t="n">
         <v>137</v>
       </c>
       <c r="D1414" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1414" t="n">
-        <v>11.278881</v>
+        <v>11.021464</v>
       </c>
       <c r="F1414" s="2" t="n">
-        <v>45244.509967356</v>
+        <v>45244.511368045</v>
       </c>
       <c r="G1414" t="inlineStr">
         <is>
@@ -35796,22 +35796,22 @@
     </row>
     <row r="1415">
       <c r="A1415" t="n">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="B1415" t="n">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="C1415" t="n">
         <v>137</v>
       </c>
       <c r="D1415" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1415" t="n">
-        <v>11.021464</v>
+        <v>20.838856</v>
       </c>
       <c r="F1415" s="2" t="n">
-        <v>45244.511368045</v>
+        <v>45244.51217165841</v>
       </c>
       <c r="G1415" t="inlineStr">
         <is>
@@ -35821,22 +35821,22 @@
     </row>
     <row r="1416">
       <c r="A1416" t="n">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B1416" t="n">
-        <v>2450</v>
+        <v>2452</v>
       </c>
       <c r="C1416" t="n">
         <v>137</v>
       </c>
       <c r="D1416" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1416" t="n">
-        <v>20.838856</v>
+        <v>11.38812</v>
       </c>
       <c r="F1416" s="2" t="n">
-        <v>45244.51217165841</v>
+        <v>45244.51322990598</v>
       </c>
       <c r="G1416" t="inlineStr">
         <is>
@@ -35846,22 +35846,22 @@
     </row>
     <row r="1417">
       <c r="A1417" t="n">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B1417" t="n">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="C1417" t="n">
         <v>137</v>
       </c>
       <c r="D1417" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1417" t="n">
-        <v>11.38812</v>
+        <v>12.46179</v>
       </c>
       <c r="F1417" s="2" t="n">
-        <v>45244.51322990598</v>
+        <v>45244.51465783417</v>
       </c>
       <c r="G1417" t="inlineStr">
         <is>
@@ -35871,22 +35871,22 @@
     </row>
     <row r="1418">
       <c r="A1418" t="n">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B1418" t="n">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="C1418" t="n">
         <v>137</v>
       </c>
       <c r="D1418" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1418" t="n">
-        <v>12.46179</v>
+        <v>11.834864</v>
       </c>
       <c r="F1418" s="2" t="n">
-        <v>45244.51465783417</v>
+        <v>45244.5153778563</v>
       </c>
       <c r="G1418" t="inlineStr">
         <is>
@@ -35896,22 +35896,22 @@
     </row>
     <row r="1419">
       <c r="A1419" t="n">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="B1419" t="n">
-        <v>2455</v>
+        <v>2457</v>
       </c>
       <c r="C1419" t="n">
         <v>137</v>
       </c>
       <c r="D1419" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1419" t="n">
-        <v>11.834864</v>
+        <v>11.856185</v>
       </c>
       <c r="F1419" s="2" t="n">
-        <v>45244.5153778563</v>
+        <v>45244.51697076253</v>
       </c>
       <c r="G1419" t="inlineStr">
         <is>
@@ -35921,22 +35921,22 @@
     </row>
     <row r="1420">
       <c r="A1420" t="n">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="B1420" t="n">
-        <v>2457</v>
+        <v>2462</v>
       </c>
       <c r="C1420" t="n">
         <v>137</v>
       </c>
       <c r="D1420" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E1420" t="n">
-        <v>11.856185</v>
+        <v>10.954654</v>
       </c>
       <c r="F1420" s="2" t="n">
-        <v>45244.51697076253</v>
+        <v>45244.52087012042</v>
       </c>
       <c r="G1420" t="inlineStr">
         <is>
@@ -35946,22 +35946,22 @@
     </row>
     <row r="1421">
       <c r="A1421" t="n">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B1421" t="n">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="C1421" t="n">
         <v>137</v>
       </c>
       <c r="D1421" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1421" t="n">
-        <v>10.954654</v>
+        <v>12.460922</v>
       </c>
       <c r="F1421" s="2" t="n">
-        <v>45244.52087012042</v>
+        <v>45244.52162541555</v>
       </c>
       <c r="G1421" t="inlineStr">
         <is>
@@ -35971,22 +35971,22 @@
     </row>
     <row r="1422">
       <c r="A1422" t="n">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B1422" t="n">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="C1422" t="n">
         <v>137</v>
       </c>
       <c r="D1422" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1422" t="n">
-        <v>12.460922</v>
+        <v>15.017374</v>
       </c>
       <c r="F1422" s="2" t="n">
-        <v>45244.52162541555</v>
+        <v>45244.52336463649</v>
       </c>
       <c r="G1422" t="inlineStr">
         <is>
@@ -35996,22 +35996,22 @@
     </row>
     <row r="1423">
       <c r="A1423" t="n">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="B1423" t="n">
-        <v>2465</v>
+        <v>2471</v>
       </c>
       <c r="C1423" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D1423" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E1423" t="n">
-        <v>15.017374</v>
+        <v>10.766345</v>
       </c>
       <c r="F1423" s="2" t="n">
-        <v>45244.52336463649</v>
+        <v>45244.53517212576</v>
       </c>
       <c r="G1423" t="inlineStr">
         <is>
@@ -36021,22 +36021,22 @@
     </row>
     <row r="1424">
       <c r="A1424" t="n">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B1424" t="n">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="C1424" t="n">
         <v>138</v>
       </c>
       <c r="D1424" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1424" t="n">
-        <v>10.766345</v>
+        <v>10.33062</v>
       </c>
       <c r="F1424" s="2" t="n">
-        <v>45244.53517212576</v>
+        <v>45244.53602807374</v>
       </c>
       <c r="G1424" t="inlineStr">
         <is>
@@ -36046,22 +36046,22 @@
     </row>
     <row r="1425">
       <c r="A1425" t="n">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B1425" t="n">
-        <v>2472</v>
+        <v>2475</v>
       </c>
       <c r="C1425" t="n">
         <v>138</v>
       </c>
       <c r="D1425" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1425" t="n">
-        <v>10.33062</v>
+        <v>10.126096</v>
       </c>
       <c r="F1425" s="2" t="n">
-        <v>45244.53602807374</v>
+        <v>45244.53814883654</v>
       </c>
       <c r="G1425" t="inlineStr">
         <is>
@@ -36071,22 +36071,22 @@
     </row>
     <row r="1426">
       <c r="A1426" t="n">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B1426" t="n">
-        <v>2475</v>
+        <v>2478</v>
       </c>
       <c r="C1426" t="n">
         <v>138</v>
       </c>
       <c r="D1426" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E1426" t="n">
-        <v>10.126096</v>
+        <v>10.442455</v>
       </c>
       <c r="F1426" s="2" t="n">
-        <v>45244.53814883654</v>
+        <v>45244.54052633754</v>
       </c>
       <c r="G1426" t="inlineStr">
         <is>
@@ -36096,22 +36096,22 @@
     </row>
     <row r="1427">
       <c r="A1427" t="n">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B1427" t="n">
-        <v>2478</v>
+        <v>2480</v>
       </c>
       <c r="C1427" t="n">
         <v>138</v>
       </c>
       <c r="D1427" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1427" t="n">
-        <v>10.442455</v>
+        <v>11.445504</v>
       </c>
       <c r="F1427" s="2" t="n">
-        <v>45244.54052633754</v>
+        <v>45244.54210331162</v>
       </c>
       <c r="G1427" t="inlineStr">
         <is>
@@ -36121,22 +36121,22 @@
     </row>
     <row r="1428">
       <c r="A1428" t="n">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="B1428" t="n">
-        <v>2480</v>
+        <v>2483</v>
       </c>
       <c r="C1428" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D1428" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E1428" t="n">
-        <v>11.445504</v>
+        <v>12.731875</v>
       </c>
       <c r="F1428" s="2" t="n">
-        <v>45244.54210331162</v>
+        <v>45244.66394612376</v>
       </c>
       <c r="G1428" t="inlineStr">
         <is>
@@ -36146,22 +36146,22 @@
     </row>
     <row r="1429">
       <c r="A1429" t="n">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B1429" t="n">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="C1429" t="n">
         <v>139</v>
       </c>
       <c r="D1429" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1429" t="n">
-        <v>12.731875</v>
+        <v>15.703808</v>
       </c>
       <c r="F1429" s="2" t="n">
-        <v>45244.66394612376</v>
+        <v>45244.66473308401</v>
       </c>
       <c r="G1429" t="inlineStr">
         <is>
@@ -36171,22 +36171,22 @@
     </row>
     <row r="1430">
       <c r="A1430" t="n">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="B1430" t="n">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="C1430" t="n">
         <v>139</v>
       </c>
       <c r="D1430" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1430" t="n">
-        <v>15.703808</v>
+        <v>12.06119</v>
       </c>
       <c r="F1430" s="2" t="n">
-        <v>45244.66473308401</v>
+        <v>45244.66527941281</v>
       </c>
       <c r="G1430" t="inlineStr">
         <is>
@@ -36196,22 +36196,22 @@
     </row>
     <row r="1431">
       <c r="A1431" t="n">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="B1431" t="n">
-        <v>2485</v>
+        <v>2492</v>
       </c>
       <c r="C1431" t="n">
         <v>139</v>
       </c>
       <c r="D1431" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E1431" t="n">
-        <v>12.06119</v>
+        <v>11.978351</v>
       </c>
       <c r="F1431" s="2" t="n">
-        <v>45244.66527941281</v>
+        <v>45244.67126001744</v>
       </c>
       <c r="G1431" t="inlineStr">
         <is>
@@ -36221,22 +36221,22 @@
     </row>
     <row r="1432">
       <c r="A1432" t="n">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B1432" t="n">
-        <v>2492</v>
+        <v>2494</v>
       </c>
       <c r="C1432" t="n">
         <v>139</v>
       </c>
       <c r="D1432" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1432" t="n">
-        <v>11.978351</v>
+        <v>12.722344</v>
       </c>
       <c r="F1432" s="2" t="n">
-        <v>45244.67126001744</v>
+        <v>45244.67348515578</v>
       </c>
       <c r="G1432" t="inlineStr">
         <is>
@@ -36246,22 +36246,22 @@
     </row>
     <row r="1433">
       <c r="A1433" t="n">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B1433" t="n">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="C1433" t="n">
         <v>139</v>
       </c>
       <c r="D1433" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1433" t="n">
-        <v>12.722344</v>
+        <v>13.371248</v>
       </c>
       <c r="F1433" s="2" t="n">
-        <v>45244.67348515578</v>
+        <v>45244.67411768078</v>
       </c>
       <c r="G1433" t="inlineStr">
         <is>
@@ -36271,22 +36271,22 @@
     </row>
     <row r="1434">
       <c r="A1434" t="n">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B1434" t="n">
-        <v>2495</v>
+        <v>2497</v>
       </c>
       <c r="C1434" t="n">
         <v>139</v>
       </c>
       <c r="D1434" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1434" t="n">
-        <v>13.371248</v>
+        <v>4.127748</v>
       </c>
       <c r="F1434" s="2" t="n">
-        <v>45244.67411768078</v>
+        <v>45244.67595144993</v>
       </c>
       <c r="G1434" t="inlineStr">
         <is>
@@ -36296,22 +36296,22 @@
     </row>
     <row r="1435">
       <c r="A1435" t="n">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B1435" t="n">
-        <v>2497</v>
+        <v>2500</v>
       </c>
       <c r="C1435" t="n">
         <v>139</v>
       </c>
       <c r="D1435" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1435" t="n">
-        <v>4.127748</v>
+        <v>13.555609</v>
       </c>
       <c r="F1435" s="2" t="n">
-        <v>45244.67595144993</v>
+        <v>45244.6784665364</v>
       </c>
       <c r="G1435" t="inlineStr">
         <is>
@@ -36321,22 +36321,22 @@
     </row>
     <row r="1436">
       <c r="A1436" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B1436" t="n">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="C1436" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D1436" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E1436" t="n">
-        <v>13.555609</v>
+        <v>13.488983</v>
       </c>
       <c r="F1436" s="2" t="n">
-        <v>45244.6784665364</v>
+        <v>45244.69004647295</v>
       </c>
       <c r="G1436" t="inlineStr">
         <is>
@@ -36346,22 +36346,22 @@
     </row>
     <row r="1437">
       <c r="A1437" t="n">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B1437" t="n">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="C1437" t="n">
         <v>140</v>
       </c>
       <c r="D1437" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E1437" t="n">
-        <v>13.488983</v>
+        <v>13.785388</v>
       </c>
       <c r="F1437" s="2" t="n">
-        <v>45244.69004647295</v>
+        <v>45244.69305991784</v>
       </c>
       <c r="G1437" t="inlineStr">
         <is>
@@ -36371,22 +36371,22 @@
     </row>
     <row r="1438">
       <c r="A1438" t="n">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B1438" t="n">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="C1438" t="n">
         <v>140</v>
       </c>
       <c r="D1438" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1438" t="n">
-        <v>13.785388</v>
+        <v>14.245088</v>
       </c>
       <c r="F1438" s="2" t="n">
-        <v>45244.69305991784</v>
+        <v>45244.69411172339</v>
       </c>
       <c r="G1438" t="inlineStr">
         <is>
@@ -36396,22 +36396,22 @@
     </row>
     <row r="1439">
       <c r="A1439" t="n">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B1439" t="n">
-        <v>2507</v>
+        <v>2510</v>
       </c>
       <c r="C1439" t="n">
         <v>140</v>
       </c>
       <c r="D1439" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1439" t="n">
-        <v>14.245088</v>
+        <v>12.436232</v>
       </c>
       <c r="F1439" s="2" t="n">
-        <v>45244.69411172339</v>
+        <v>45244.69636934702</v>
       </c>
       <c r="G1439" t="inlineStr">
         <is>
@@ -36421,22 +36421,22 @@
     </row>
     <row r="1440">
       <c r="A1440" t="n">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B1440" t="n">
-        <v>2510</v>
+        <v>2513</v>
       </c>
       <c r="C1440" t="n">
         <v>140</v>
       </c>
       <c r="D1440" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E1440" t="n">
-        <v>12.436232</v>
+        <v>14.126808</v>
       </c>
       <c r="F1440" s="2" t="n">
-        <v>45244.69636934702</v>
+        <v>45244.69860266581</v>
       </c>
       <c r="G1440" t="inlineStr">
         <is>
@@ -36446,22 +36446,22 @@
     </row>
     <row r="1441">
       <c r="A1441" t="n">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="B1441" t="n">
-        <v>2513</v>
+        <v>2521</v>
       </c>
       <c r="C1441" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D1441" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E1441" t="n">
-        <v>14.126808</v>
+        <v>10.628388</v>
       </c>
       <c r="F1441" s="2" t="n">
-        <v>45244.69860266581</v>
+        <v>45244.72191700818</v>
       </c>
       <c r="G1441" t="inlineStr">
         <is>
@@ -36471,22 +36471,22 @@
     </row>
     <row r="1442">
       <c r="A1442" t="n">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B1442" t="n">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="C1442" t="n">
         <v>141</v>
       </c>
       <c r="D1442" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1442" t="n">
-        <v>10.628388</v>
+        <v>9.394917</v>
       </c>
       <c r="F1442" s="2" t="n">
-        <v>45244.72191700818</v>
+        <v>45244.72300103514</v>
       </c>
       <c r="G1442" t="inlineStr">
         <is>
@@ -36496,22 +36496,22 @@
     </row>
     <row r="1443">
       <c r="A1443" t="n">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B1443" t="n">
-        <v>2522</v>
+        <v>2525</v>
       </c>
       <c r="C1443" t="n">
         <v>141</v>
       </c>
       <c r="D1443" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1443" t="n">
-        <v>9.394917</v>
+        <v>10.660724</v>
       </c>
       <c r="F1443" s="2" t="n">
-        <v>45244.72300103514</v>
+        <v>45244.72519393238</v>
       </c>
       <c r="G1443" t="inlineStr">
         <is>
@@ -36521,22 +36521,22 @@
     </row>
     <row r="1444">
       <c r="A1444" t="n">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="B1444" t="n">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="C1444" t="n">
         <v>141</v>
       </c>
       <c r="D1444" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1444" t="n">
-        <v>10.660724</v>
+        <v>15.537527</v>
       </c>
       <c r="F1444" s="2" t="n">
-        <v>45244.72519393238</v>
+        <v>45244.72630750982</v>
       </c>
       <c r="G1444" t="inlineStr">
         <is>
@@ -36546,22 +36546,22 @@
     </row>
     <row r="1445">
       <c r="A1445" t="n">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B1445" t="n">
-        <v>2526</v>
+        <v>2528</v>
       </c>
       <c r="C1445" t="n">
         <v>141</v>
       </c>
       <c r="D1445" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1445" t="n">
-        <v>15.537527</v>
+        <v>10.354641</v>
       </c>
       <c r="F1445" s="2" t="n">
-        <v>45244.72630750982</v>
+        <v>45244.72761791138</v>
       </c>
       <c r="G1445" t="inlineStr">
         <is>
@@ -36571,22 +36571,22 @@
     </row>
     <row r="1446">
       <c r="A1446" t="n">
-        <v>1444</v>
+        <v>1459</v>
       </c>
       <c r="B1446" t="n">
-        <v>2528</v>
+        <v>2555</v>
       </c>
       <c r="C1446" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D1446" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E1446" t="n">
-        <v>10.354641</v>
+        <v>20.997644</v>
       </c>
       <c r="F1446" s="2" t="n">
-        <v>45244.72761791138</v>
+        <v>45244.78568444613</v>
       </c>
       <c r="G1446" t="inlineStr">
         <is>
@@ -36596,22 +36596,22 @@
     </row>
     <row r="1447">
       <c r="A1447" t="n">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B1447" t="n">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="C1447" t="n">
         <v>143</v>
       </c>
       <c r="D1447" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1447" t="n">
-        <v>20.997644</v>
+        <v>11.183741</v>
       </c>
       <c r="F1447" s="2" t="n">
-        <v>45244.78568444613</v>
+        <v>45244.78621478076</v>
       </c>
       <c r="G1447" t="inlineStr">
         <is>
@@ -36621,22 +36621,22 @@
     </row>
     <row r="1448">
       <c r="A1448" t="n">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B1448" t="n">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="C1448" t="n">
         <v>143</v>
       </c>
       <c r="D1448" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1448" t="n">
-        <v>11.183741</v>
+        <v>11.637844</v>
       </c>
       <c r="F1448" s="2" t="n">
-        <v>45244.78621478076</v>
+        <v>45244.78706788708</v>
       </c>
       <c r="G1448" t="inlineStr">
         <is>
@@ -36646,22 +36646,22 @@
     </row>
     <row r="1449">
       <c r="A1449" t="n">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B1449" t="n">
-        <v>2557</v>
+        <v>2560</v>
       </c>
       <c r="C1449" t="n">
         <v>143</v>
       </c>
       <c r="D1449" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1449" t="n">
-        <v>11.637844</v>
+        <v>11.682506</v>
       </c>
       <c r="F1449" s="2" t="n">
-        <v>45244.78706788708</v>
+        <v>45244.78958109798</v>
       </c>
       <c r="G1449" t="inlineStr">
         <is>
@@ -36671,22 +36671,22 @@
     </row>
     <row r="1450">
       <c r="A1450" t="n">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="B1450" t="n">
-        <v>2560</v>
+        <v>2565</v>
       </c>
       <c r="C1450" t="n">
         <v>143</v>
       </c>
       <c r="D1450" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E1450" t="n">
-        <v>11.682506</v>
+        <v>11.633062</v>
       </c>
       <c r="F1450" s="2" t="n">
-        <v>45244.78958109798</v>
+        <v>45244.79353475094</v>
       </c>
       <c r="G1450" t="inlineStr">
         <is>
@@ -36696,22 +36696,22 @@
     </row>
     <row r="1451">
       <c r="A1451" t="n">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B1451" t="n">
-        <v>2565</v>
+        <v>2567</v>
       </c>
       <c r="C1451" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D1451" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E1451" t="n">
-        <v>11.633062</v>
+        <v>15.490917</v>
       </c>
       <c r="F1451" s="2" t="n">
-        <v>45244.79353475094</v>
+        <v>45244.80537572999</v>
       </c>
       <c r="G1451" t="inlineStr">
         <is>
@@ -36721,22 +36721,22 @@
     </row>
     <row r="1452">
       <c r="A1452" t="n">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B1452" t="n">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="C1452" t="n">
         <v>144</v>
       </c>
       <c r="D1452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1452" t="n">
-        <v>15.490917</v>
+        <v>16.896564</v>
       </c>
       <c r="F1452" s="2" t="n">
-        <v>45244.80537572999</v>
+        <v>45244.80625522072</v>
       </c>
       <c r="G1452" t="inlineStr">
         <is>
@@ -36746,22 +36746,22 @@
     </row>
     <row r="1453">
       <c r="A1453" t="n">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B1453" t="n">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="C1453" t="n">
         <v>144</v>
       </c>
       <c r="D1453" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1453" t="n">
-        <v>16.896564</v>
+        <v>12.111812</v>
       </c>
       <c r="F1453" s="2" t="n">
-        <v>45244.80625522072</v>
+        <v>45244.80675646979</v>
       </c>
       <c r="G1453" t="inlineStr">
         <is>
@@ -36771,22 +36771,22 @@
     </row>
     <row r="1454">
       <c r="A1454" t="n">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B1454" t="n">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="C1454" t="n">
         <v>144</v>
       </c>
       <c r="D1454" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1454" t="n">
-        <v>12.111812</v>
+        <v>21.178463</v>
       </c>
       <c r="F1454" s="2" t="n">
-        <v>45244.80675646979</v>
+        <v>45244.80777349558</v>
       </c>
       <c r="G1454" t="inlineStr">
         <is>
@@ -36796,22 +36796,22 @@
     </row>
     <row r="1455">
       <c r="A1455" t="n">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B1455" t="n">
-        <v>2570</v>
+        <v>2574</v>
       </c>
       <c r="C1455" t="n">
         <v>144</v>
       </c>
       <c r="D1455" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E1455" t="n">
-        <v>21.178463</v>
+        <v>13.078219</v>
       </c>
       <c r="F1455" s="2" t="n">
-        <v>45244.80777349558</v>
+        <v>45244.81056145292</v>
       </c>
       <c r="G1455" t="inlineStr">
         <is>
